--- a/Tabelas_Oficiais/tabela_tjmg.xlsx
+++ b/Tabelas_Oficiais/tabela_tjmg.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\11 - 2026\CADEJ - INDICADORES ECONÔMICOS\20 - TABELAS DE FATORES DE ATUALIZAÇÃO MONETÁRIA DO ÍNDICE DA CGJ\09 - Setembro - 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\11 - 2026\CADEJ - INDICADORES ECONÔMICOS\20 - TABELAS DE FATORES DE ATUALIZAÇÃO MONETÁRIA DO ÍNDICE DA CGJ\10 - Outubro de 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC9C3443-6537-474E-9FD4-AA46B96FEC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63F189C9-A355-4636-97E2-5F3581371956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="83">
   <si>
     <t>ANO</t>
   </si>
@@ -57,7 +57,7 @@
     <t>CONTADORIA JUDICIAL DA COMARCA DE BELO HORIZONTE</t>
   </si>
   <si>
-    <t>Tabela Válida para: SETEMBRO DE 2026</t>
+    <t>Tabela Válida para: OUTUBRO DE 2026</t>
   </si>
   <si>
     <t>Fatores de Atualização Monetária Baseados em: ICGJ (TJMG)</t>
@@ -750,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C752"/>
+  <dimension ref="A1:C753"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" style="2" customWidth="1" collapsed="1"/>
@@ -827,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="3">
-        <v>3.2567E-3</v>
+        <v>3.2834000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -838,7 +838,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="3">
-        <v>3.2567E-3</v>
+        <v>3.2834000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -849,7 +849,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>3.2567E-3</v>
+        <v>3.2834000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -860,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8820999999999999E-3</v>
+        <v>2.9057000000000002E-3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -871,7 +871,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8820999999999999E-3</v>
+        <v>2.9057000000000002E-3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8820999999999999E-3</v>
+        <v>2.9057000000000002E-3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -893,7 +893,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4304999999999999E-3</v>
+        <v>2.4504000000000001E-3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -904,7 +904,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="3">
-        <v>2.4304999999999999E-3</v>
+        <v>2.4504000000000001E-3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -915,7 +915,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="3">
-        <v>2.4304999999999999E-3</v>
+        <v>2.4504000000000001E-3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -926,7 +926,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="3">
-        <v>2.1427E-3</v>
+        <v>2.1603E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -937,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="3">
-        <v>2.1427E-3</v>
+        <v>2.1603E-3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -948,7 +948,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="3">
-        <v>2.0742E-3</v>
+        <v>2.0912000000000001E-3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -959,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="3">
-        <v>2.0487000000000001E-3</v>
+        <v>2.0655000000000001E-3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="3">
-        <v>2.0300000000000001E-3</v>
+        <v>2.0466E-3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -981,7 +981,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="3">
-        <v>1.9981E-3</v>
+        <v>2.0144999999999998E-3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -992,7 +992,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="3">
-        <v>1.9615000000000001E-3</v>
+        <v>1.9775999999999999E-3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1003,7 +1003,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="3">
-        <v>1.9105000000000001E-3</v>
+        <v>1.9262000000000001E-3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1014,7 +1014,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="3">
-        <v>1.8833000000000001E-3</v>
+        <v>1.8986999999999999E-3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1025,7 +1025,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="3">
-        <v>1.851E-3</v>
+        <v>1.8661999999999999E-3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1036,7 +1036,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="3">
-        <v>1.7814E-3</v>
+        <v>1.7960000000000001E-3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1047,7 +1047,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="3">
-        <v>1.7057999999999999E-3</v>
+        <v>1.7198000000000001E-3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1058,7 +1058,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="3">
-        <v>1.6387999999999999E-3</v>
+        <v>1.6521999999999999E-3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1069,7 +1069,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="3">
-        <v>1.5942E-3</v>
+        <v>1.6073000000000001E-3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1080,7 +1080,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="3">
-        <v>1.5495999999999999E-3</v>
+        <v>1.5623E-3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1091,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="C34" s="3">
-        <v>1.5073E-3</v>
+        <v>1.5196999999999999E-3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1102,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="3">
-        <v>1.4679000000000001E-3</v>
+        <v>1.4798999999999999E-3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="3">
-        <v>1.436E-3</v>
+        <v>1.4478E-3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
       <c r="C37" s="3">
-        <v>1.4017999999999999E-3</v>
+        <v>1.4132999999999999E-3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="C38" s="3">
-        <v>1.3697234</v>
+        <v>1.3809551</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
       <c r="C39" s="3">
-        <v>1.3415172</v>
+        <v>1.3525176000000001</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="3">
-        <v>1.3219163</v>
+        <v>1.3327560000000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="3">
-        <v>1.3023604</v>
+        <v>1.3130398000000001</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1179,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="C42" s="3">
-        <v>1.2793403999999999</v>
+        <v>1.2898309999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1190,7 +1190,7 @@
         <v>19</v>
       </c>
       <c r="C43" s="3">
-        <v>1.2441567</v>
+        <v>1.2543588000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1201,7 +1201,7 @@
         <v>20</v>
       </c>
       <c r="C44" s="3">
-        <v>1.2135621999999999</v>
+        <v>1.2235134000000001</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
         <v>21</v>
       </c>
       <c r="C45" s="3">
-        <v>1.1953034</v>
+        <v>1.2051049</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="C46" s="3">
-        <v>1.1896282</v>
+        <v>1.1993832</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1234,7 +1234,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="3">
-        <v>1.1814298000000001</v>
+        <v>1.1911175000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="3">
-        <v>1.1649501</v>
+        <v>1.1745026999999999</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1256,7 +1256,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="3">
-        <v>1.1436809999999999</v>
+        <v>1.1530592</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1267,7 +1267,7 @@
         <v>14</v>
       </c>
       <c r="C50" s="3">
-        <v>1.1239478000000001</v>
+        <v>1.1331642</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1278,7 +1278,7 @@
         <v>15</v>
       </c>
       <c r="C51" s="3">
-        <v>1.1078923000000001</v>
+        <v>1.1169770000000001</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1289,7 +1289,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="3">
-        <v>1.0919217000000001</v>
+        <v>1.1008754999999999</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1300,7 +1300,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="3">
-        <v>1.0718003</v>
+        <v>1.0805891000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1311,7 +1311,7 @@
         <v>18</v>
       </c>
       <c r="C54" s="3">
-        <v>1.0439750000000001</v>
+        <v>1.0525355999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1322,7 +1322,7 @@
         <v>19</v>
       </c>
       <c r="C55" s="3">
-        <v>1.0150207</v>
+        <v>1.0233439</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1333,7 +1333,7 @@
         <v>20</v>
       </c>
       <c r="C56" s="3">
-        <v>0.99274620000000002</v>
+        <v>1.0008866999999999</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1344,7 +1344,7 @@
         <v>21</v>
       </c>
       <c r="C57" s="3">
-        <v>0.97491830000000002</v>
+        <v>0.98291260000000003</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1355,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="C58" s="3">
-        <v>0.96139419999999998</v>
+        <v>0.96927759999999996</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1366,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="C59" s="3">
-        <v>0.94713619999999998</v>
+        <v>0.95490269999999999</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1377,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="C60" s="3">
-        <v>0.93196100000000004</v>
+        <v>0.93960310000000002</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1388,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="C61" s="3">
-        <v>0.91443099999999999</v>
+        <v>0.92192929999999995</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1399,7 +1399,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="3">
-        <v>0.89804360000000005</v>
+        <v>0.90540759999999998</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1410,7 +1410,7 @@
         <v>15</v>
       </c>
       <c r="C63" s="3">
-        <v>0.88247120000000001</v>
+        <v>0.88970749999999998</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1421,7 +1421,7 @@
         <v>16</v>
       </c>
       <c r="C64" s="3">
-        <v>0.87021119999999996</v>
+        <v>0.87734690000000004</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1432,7 +1432,7 @@
         <v>17</v>
       </c>
       <c r="C65" s="3">
-        <v>0.85693330000000001</v>
+        <v>0.86396019999999996</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
         <v>18</v>
       </c>
       <c r="C66" s="3">
-        <v>0.84646690000000002</v>
+        <v>0.8534079</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>19</v>
       </c>
       <c r="C67" s="3">
-        <v>0.83517940000000002</v>
+        <v>0.84202790000000005</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1465,7 +1465,7 @@
         <v>20</v>
       </c>
       <c r="C68" s="3">
-        <v>0.82943750000000005</v>
+        <v>0.83623890000000001</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="C69" s="3">
-        <v>0.82335760000000002</v>
+        <v>0.83010910000000004</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1487,7 +1487,7 @@
         <v>9</v>
       </c>
       <c r="C70" s="3">
-        <v>0.8159322</v>
+        <v>0.82262279999999999</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1498,7 +1498,7 @@
         <v>10</v>
       </c>
       <c r="C71" s="3">
-        <v>0.8028592</v>
+        <v>0.80944260000000001</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1509,7 +1509,7 @@
         <v>11</v>
       </c>
       <c r="C72" s="3">
-        <v>0.78638459999999999</v>
+        <v>0.79283300000000001</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
       <c r="C73" s="3">
-        <v>0.76911510000000005</v>
+        <v>0.77542180000000005</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1531,7 +1531,7 @@
         <v>14</v>
       </c>
       <c r="C74" s="3">
-        <v>0.7522413</v>
+        <v>0.75840969999999996</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1542,7 +1542,7 @@
         <v>15</v>
       </c>
       <c r="C75" s="3">
-        <v>0.73742410000000003</v>
+        <v>0.74347099999999999</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1553,7 +1553,7 @@
         <v>16</v>
       </c>
       <c r="C76" s="3">
-        <v>0.72916990000000004</v>
+        <v>0.7351491</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1564,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="C77" s="3">
-        <v>0.72253889999999998</v>
+        <v>0.72846370000000005</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>18</v>
       </c>
       <c r="C78" s="3">
-        <v>0.71586879999999997</v>
+        <v>0.72173889999999996</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1586,7 +1586,7 @@
         <v>19</v>
       </c>
       <c r="C79" s="3">
-        <v>0.70502290000000001</v>
+        <v>0.71080410000000005</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1597,7 +1597,7 @@
         <v>20</v>
       </c>
       <c r="C80" s="3">
-        <v>0.69882120000000003</v>
+        <v>0.7045515</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1608,7 +1608,7 @@
         <v>21</v>
       </c>
       <c r="C81" s="3">
-        <v>0.69228559999999995</v>
+        <v>0.69796230000000004</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1619,7 +1619,7 @@
         <v>9</v>
       </c>
       <c r="C82" s="3">
-        <v>0.68414280000000005</v>
+        <v>0.68975280000000005</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1630,7 +1630,7 @@
         <v>10</v>
       </c>
       <c r="C83" s="3">
-        <v>0.67144959999999998</v>
+        <v>0.67695550000000004</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1641,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="3">
-        <v>0.65748859999999998</v>
+        <v>0.66288000000000002</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
         <v>13</v>
       </c>
       <c r="C85" s="3">
-        <v>0.64486279999999996</v>
+        <v>0.65015069999999997</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -1663,7 +1663,7 @@
         <v>14</v>
       </c>
       <c r="C86" s="3">
-        <v>0.63320449999999995</v>
+        <v>0.63839679999999999</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
         <v>15</v>
       </c>
       <c r="C87" s="3">
-        <v>0.62494349999999999</v>
+        <v>0.63006799999999996</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -1685,7 +1685,7 @@
         <v>16</v>
       </c>
       <c r="C88" s="3">
-        <v>0.61876940000000002</v>
+        <v>0.62384329999999999</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="C89" s="3">
-        <v>0.61168140000000004</v>
+        <v>0.61669719999999995</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
         <v>18</v>
       </c>
       <c r="C90" s="3">
-        <v>0.60307449999999996</v>
+        <v>0.60801970000000005</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -1718,7 +1718,7 @@
         <v>19</v>
       </c>
       <c r="C91" s="3">
-        <v>0.5913583</v>
+        <v>0.59620740000000005</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -1729,7 +1729,7 @@
         <v>20</v>
       </c>
       <c r="C92" s="3">
-        <v>0.57977909999999999</v>
+        <v>0.58453330000000003</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -1740,7 +1740,7 @@
         <v>21</v>
       </c>
       <c r="C93" s="3">
-        <v>0.56785280000000005</v>
+        <v>0.57250920000000005</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -1751,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="C94" s="3">
-        <v>0.55574210000000002</v>
+        <v>0.5602992</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -1762,7 +1762,7 @@
         <v>10</v>
       </c>
       <c r="C95" s="3">
-        <v>0.54477379999999997</v>
+        <v>0.54924090000000003</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -1773,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="C96" s="3">
-        <v>0.53598880000000004</v>
+        <v>0.54038390000000003</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -1784,7 +1784,7 @@
         <v>13</v>
       </c>
       <c r="C97" s="3">
-        <v>0.52945450000000005</v>
+        <v>0.53379600000000005</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>14</v>
       </c>
       <c r="C98" s="3">
-        <v>0.52316149999999995</v>
+        <v>0.52745140000000001</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -1806,7 +1806,7 @@
         <v>15</v>
       </c>
       <c r="C99" s="3">
-        <v>0.51627840000000003</v>
+        <v>0.52051190000000003</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -1817,7 +1817,7 @@
         <v>16</v>
       </c>
       <c r="C100" s="3">
-        <v>0.51045399999999996</v>
+        <v>0.51463970000000003</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -1828,7 +1828,7 @@
         <v>17</v>
       </c>
       <c r="C101" s="3">
-        <v>0.50374300000000005</v>
+        <v>0.50787369999999998</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -1839,7 +1839,7 @@
         <v>18</v>
       </c>
       <c r="C102" s="3">
-        <v>0.49539250000000001</v>
+        <v>0.49945469999999997</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -1850,7 +1850,7 @@
         <v>19</v>
       </c>
       <c r="C103" s="3">
-        <v>0.48665750000000002</v>
+        <v>0.49064809999999998</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -1861,7 +1861,7 @@
         <v>20</v>
       </c>
       <c r="C104" s="3">
-        <v>0.4797766</v>
+        <v>0.4837108</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="C105" s="3">
-        <v>0.4757826</v>
+        <v>0.479684</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -1883,7 +1883,7 @@
         <v>9</v>
       </c>
       <c r="C106" s="3">
-        <v>0.47240090000000001</v>
+        <v>0.47627459999999999</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -1894,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="C107" s="3">
-        <v>0.4679217</v>
+        <v>0.47175869999999998</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -1905,7 +1905,7 @@
         <v>11</v>
       </c>
       <c r="C108" s="3">
-        <v>0.46484940000000002</v>
+        <v>0.4686612</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -1916,7 +1916,7 @@
         <v>13</v>
       </c>
       <c r="C109" s="3">
-        <v>0.45960269999999998</v>
+        <v>0.46337139999999999</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -1927,7 +1927,7 @@
         <v>14</v>
       </c>
       <c r="C110" s="3">
-        <v>0.45510719999999999</v>
+        <v>0.4588391</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
         <v>15</v>
       </c>
       <c r="C111" s="3">
-        <v>0.4503875</v>
+        <v>0.4540807</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="C112" s="3">
-        <v>0.44503359999999997</v>
+        <v>0.4486829</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -1960,7 +1960,7 @@
         <v>17</v>
       </c>
       <c r="C113" s="3">
-        <v>0.43998419999999999</v>
+        <v>0.44359209999999999</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -1971,7 +1971,7 @@
         <v>18</v>
       </c>
       <c r="C114" s="3">
-        <v>0.43446620000000002</v>
+        <v>0.4380288</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -1982,7 +1982,7 @@
         <v>19</v>
       </c>
       <c r="C115" s="3">
-        <v>0.42970969999999997</v>
+        <v>0.43323329999999999</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -1993,7 +1993,7 @@
         <v>20</v>
       </c>
       <c r="C116" s="3">
-        <v>0.42588939999999997</v>
+        <v>0.42938169999999998</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2004,7 +2004,7 @@
         <v>21</v>
       </c>
       <c r="C117" s="3">
-        <v>0.42235479999999997</v>
+        <v>0.42581809999999998</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2015,7 +2015,7 @@
         <v>9</v>
       </c>
       <c r="C118" s="3">
-        <v>0.41828769999999998</v>
+        <v>0.42171769999999997</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2026,7 +2026,7 @@
         <v>10</v>
       </c>
       <c r="C119" s="3">
-        <v>0.41545979999999999</v>
+        <v>0.41886659999999998</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2037,7 +2037,7 @@
         <v>11</v>
       </c>
       <c r="C120" s="3">
-        <v>0.41193960000000002</v>
+        <v>0.41531750000000001</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2048,7 +2048,7 @@
         <v>13</v>
       </c>
       <c r="C121" s="3">
-        <v>0.40401900000000002</v>
+        <v>0.40733200000000003</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2059,7 +2059,7 @@
         <v>14</v>
       </c>
       <c r="C122" s="3">
-        <v>0.3998042</v>
+        <v>0.40308260000000001</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2070,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="C123" s="3">
-        <v>0.39390550000000002</v>
+        <v>0.39713549999999997</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -2081,7 +2081,7 @@
         <v>16</v>
       </c>
       <c r="C124" s="3">
-        <v>0.38901210000000003</v>
+        <v>0.392202</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2092,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="C125" s="3">
-        <v>0.38275009999999998</v>
+        <v>0.38588869999999997</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -2103,7 +2103,7 @@
         <v>18</v>
       </c>
       <c r="C126" s="3">
-        <v>0.37477909999999998</v>
+        <v>0.37785229999999997</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2114,7 +2114,7 @@
         <v>19</v>
       </c>
       <c r="C127" s="3">
-        <v>0.36271759999999997</v>
+        <v>0.36569190000000001</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2125,7 +2125,7 @@
         <v>20</v>
       </c>
       <c r="C128" s="3">
-        <v>0.34743499999999999</v>
+        <v>0.35028399999999998</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2136,7 +2136,7 @@
         <v>21</v>
       </c>
       <c r="C129" s="3">
-        <v>0.33162249999999999</v>
+        <v>0.33434180000000002</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2147,7 +2147,7 @@
         <v>9</v>
       </c>
       <c r="C130" s="3">
-        <v>0.31964609999999999</v>
+        <v>0.32226719999999998</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2158,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="C131" s="3">
-        <v>0.31289139999999999</v>
+        <v>0.31545709999999999</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2169,7 +2169,7 @@
         <v>11</v>
       </c>
       <c r="C132" s="3">
-        <v>0.30900290000000002</v>
+        <v>0.3115367</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>13</v>
       </c>
       <c r="C133" s="3">
-        <v>0.30509530000000001</v>
+        <v>0.30759710000000001</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2191,7 +2191,7 @@
         <v>14</v>
       </c>
       <c r="C134" s="3">
-        <v>0.30053590000000002</v>
+        <v>0.3030003</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2202,7 +2202,7 @@
         <v>15</v>
       </c>
       <c r="C135" s="3">
-        <v>0.29562579999999999</v>
+        <v>0.29804989999999998</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2213,7 +2213,7 @@
         <v>16</v>
       </c>
       <c r="C136" s="3">
-        <v>0.29017419999999999</v>
+        <v>0.29255360000000002</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2224,7 +2224,7 @@
         <v>17</v>
       </c>
       <c r="C137" s="3">
-        <v>0.28449600000000003</v>
+        <v>0.2868289</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2235,7 +2235,7 @@
         <v>18</v>
       </c>
       <c r="C138" s="3">
-        <v>0.27808430000000001</v>
+        <v>0.28036460000000002</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -2246,7 +2246,7 @@
         <v>19</v>
       </c>
       <c r="C139" s="3">
-        <v>0.27309549999999999</v>
+        <v>0.27533489999999999</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2257,7 +2257,7 @@
         <v>20</v>
       </c>
       <c r="C140" s="3">
-        <v>0.26850200000000002</v>
+        <v>0.27070369999999999</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2268,7 +2268,7 @@
         <v>21</v>
       </c>
       <c r="C141" s="3">
-        <v>0.26438309999999998</v>
+        <v>0.26655099999999998</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -2279,7 +2279,7 @@
         <v>9</v>
       </c>
       <c r="C142" s="3">
-        <v>0.25912499999999999</v>
+        <v>0.26124979999999998</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>10</v>
       </c>
       <c r="C143" s="3">
-        <v>0.25361650000000002</v>
+        <v>0.25569619999999998</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2301,7 +2301,7 @@
         <v>11</v>
       </c>
       <c r="C144" s="3">
-        <v>0.248774</v>
+        <v>0.25081389999999998</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -2312,7 +2312,7 @@
         <v>13</v>
       </c>
       <c r="C145" s="3">
-        <v>0.2442783</v>
+        <v>0.24628140000000001</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -2323,7 +2323,7 @@
         <v>14</v>
       </c>
       <c r="C146" s="3">
-        <v>0.23967640000000001</v>
+        <v>0.24164169999999999</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -2334,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="C147" s="3">
-        <v>0.23443259999999999</v>
+        <v>0.23635490000000001</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -2345,7 +2345,7 @@
         <v>16</v>
       </c>
       <c r="C148" s="3">
-        <v>0.22899430000000001</v>
+        <v>0.2308721</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -2356,7 +2356,7 @@
         <v>17</v>
       </c>
       <c r="C149" s="3">
-        <v>0.22335650000000001</v>
+        <v>0.225188</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -2367,7 +2367,7 @@
         <v>18</v>
       </c>
       <c r="C150" s="3">
-        <v>0.2169006</v>
+        <v>0.21867919999999999</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -2378,7 +2378,7 @@
         <v>19</v>
       </c>
       <c r="C151" s="3">
-        <v>0.2106855</v>
+        <v>0.21241309999999999</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -2389,7 +2389,7 @@
         <v>20</v>
       </c>
       <c r="C152" s="3">
-        <v>0.20543649999999999</v>
+        <v>0.2071211</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -2400,7 +2400,7 @@
         <v>21</v>
       </c>
       <c r="C153" s="3">
-        <v>0.1998653</v>
+        <v>0.20150419999999999</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -2411,7 +2411,7 @@
         <v>9</v>
       </c>
       <c r="C154" s="3">
-        <v>0.19350139999999999</v>
+        <v>0.19508809999999999</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -2422,7 +2422,7 @@
         <v>10</v>
       </c>
       <c r="C155" s="3">
-        <v>0.1867664</v>
+        <v>0.18829789999999999</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -2433,7 +2433,7 @@
         <v>11</v>
       </c>
       <c r="C156" s="3">
-        <v>0.1812773</v>
+        <v>0.1827638</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -2444,7 +2444,7 @@
         <v>13</v>
       </c>
       <c r="C157" s="3">
-        <v>0.17735899999999999</v>
+        <v>0.17881330000000001</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -2455,7 +2455,7 @@
         <v>14</v>
       </c>
       <c r="C158" s="3">
-        <v>0.17434079999999999</v>
+        <v>0.17577039999999999</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -2466,7 +2466,7 @@
         <v>15</v>
       </c>
       <c r="C159" s="3">
-        <v>0.17097219999999999</v>
+        <v>0.17237420000000001</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -2477,7 +2477,7 @@
         <v>16</v>
       </c>
       <c r="C160" s="3">
-        <v>0.16718169999999999</v>
+        <v>0.1685526</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -2488,7 +2488,7 @@
         <v>17</v>
       </c>
       <c r="C161" s="3">
-        <v>0.16249520000000001</v>
+        <v>0.16382769999999999</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -2499,7 +2499,7 @@
         <v>18</v>
       </c>
       <c r="C162" s="3">
-        <v>0.1574294</v>
+        <v>0.15872030000000001</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -2510,7 +2510,7 @@
         <v>19</v>
       </c>
       <c r="C163" s="3">
-        <v>0.15234790000000001</v>
+        <v>0.15359719999999999</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -2521,7 +2521,7 @@
         <v>20</v>
       </c>
       <c r="C164" s="3">
-        <v>0.1483854</v>
+        <v>0.14960219999999999</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -2532,7 +2532,7 @@
         <v>21</v>
       </c>
       <c r="C165" s="3">
-        <v>0.1454047</v>
+        <v>0.14659700000000001</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -2543,7 +2543,7 @@
         <v>9</v>
       </c>
       <c r="C166" s="3">
-        <v>0.1433943</v>
+        <v>0.14457010000000001</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -2554,7 +2554,7 @@
         <v>10</v>
       </c>
       <c r="C167" s="3">
-        <v>0.14143310000000001</v>
+        <v>0.14259289999999999</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -2565,7 +2565,7 @@
         <v>11</v>
       </c>
       <c r="C168" s="3">
-        <v>0.13935159999999999</v>
+        <v>0.14049429999999999</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -2576,7 +2576,7 @@
         <v>13</v>
       </c>
       <c r="C169" s="3">
-        <v>0.13667309999999999</v>
+        <v>0.13779379999999999</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -2587,7 +2587,7 @@
         <v>14</v>
       </c>
       <c r="C170" s="3">
-        <v>0.13384879999999999</v>
+        <v>0.13494639999999999</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -2598,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="C171" s="3">
-        <v>0.1308165</v>
+        <v>0.13188920000000001</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -2609,7 +2609,7 @@
         <v>16</v>
       </c>
       <c r="C172" s="3">
-        <v>0.12752939999999999</v>
+        <v>0.1285751</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -2620,7 +2620,7 @@
         <v>17</v>
       </c>
       <c r="C173" s="3">
-        <v>0.1239092</v>
+        <v>0.1249253</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -2631,7 +2631,7 @@
         <v>18</v>
       </c>
       <c r="C174" s="3">
-        <v>0.1202457</v>
+        <v>0.1212317</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -2642,7 +2642,7 @@
         <v>19</v>
       </c>
       <c r="C175" s="3">
-        <v>0.11672879999999999</v>
+        <v>0.117686</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -2653,7 +2653,7 @@
         <v>20</v>
       </c>
       <c r="C176" s="3">
-        <v>0.1132624</v>
+        <v>0.11419120000000001</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -2664,7 +2664,7 @@
         <v>21</v>
       </c>
       <c r="C177" s="3">
-        <v>0.1102007</v>
+        <v>0.1111043</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -2675,7 +2675,7 @@
         <v>9</v>
       </c>
       <c r="C178" s="3">
-        <v>0.10739600000000001</v>
+        <v>0.1082766</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -2686,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="C179" s="3">
-        <v>0.1049054</v>
+        <v>0.1057656</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -2697,7 +2697,7 @@
         <v>11</v>
       </c>
       <c r="C180" s="3">
-        <v>0.1022861</v>
+        <v>0.1031248</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="3">
-        <v>9.9663799999999997E-2</v>
+        <v>0.100481</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -2719,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="C182" s="3">
-        <v>9.7462900000000005E-2</v>
+        <v>9.8262100000000005E-2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -2730,7 +2730,7 @@
         <v>15</v>
       </c>
       <c r="C183" s="3">
-        <v>9.5247899999999996E-2</v>
+        <v>9.60289E-2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,7 +2741,7 @@
         <v>16</v>
       </c>
       <c r="C184" s="3">
-        <v>9.2927399999999993E-2</v>
+        <v>9.3689400000000006E-2</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -2752,7 +2752,7 @@
         <v>17</v>
       </c>
       <c r="C185" s="3">
-        <v>8.9572200000000005E-2</v>
+        <v>9.0306700000000004E-2</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -2763,7 +2763,7 @@
         <v>18</v>
       </c>
       <c r="C186" s="3">
-        <v>8.6273799999999998E-2</v>
+        <v>8.6981199999999995E-2</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -2774,7 +2774,7 @@
         <v>19</v>
       </c>
       <c r="C187" s="3">
-        <v>8.3496000000000001E-2</v>
+        <v>8.4180699999999997E-2</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,7 +2785,7 @@
         <v>20</v>
       </c>
       <c r="C188" s="3">
-        <v>8.1285899999999994E-2</v>
+        <v>8.1952399999999995E-2</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,7 +2796,7 @@
         <v>21</v>
       </c>
       <c r="C189" s="3">
-        <v>7.9012399999999997E-2</v>
+        <v>7.9660300000000003E-2</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,7 +2807,7 @@
         <v>9</v>
       </c>
       <c r="C190" s="3">
-        <v>7.5960700000000006E-2</v>
+        <v>7.6583600000000002E-2</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -2818,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="C191" s="3">
-        <v>7.2629299999999994E-2</v>
+        <v>7.3224899999999996E-2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -2829,7 +2829,7 @@
         <v>11</v>
       </c>
       <c r="C192" s="3">
-        <v>6.9493399999999997E-2</v>
+        <v>7.0063200000000006E-2</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -2840,7 +2840,7 @@
         <v>13</v>
       </c>
       <c r="C193" s="3">
-        <v>6.6770099999999999E-2</v>
+        <v>6.7317600000000005E-2</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -2851,7 +2851,7 @@
         <v>14</v>
       </c>
       <c r="C194" s="3">
-        <v>6.4077400000000007E-2</v>
+        <v>6.4602800000000002E-2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -2862,7 +2862,7 @@
         <v>15</v>
       </c>
       <c r="C195" s="3">
-        <v>6.1790699999999997E-2</v>
+        <v>6.2297400000000003E-2</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -2873,7 +2873,7 @@
         <v>16</v>
       </c>
       <c r="C196" s="3">
-        <v>5.9586399999999998E-2</v>
+        <v>6.0075000000000003E-2</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,7 +2884,7 @@
         <v>17</v>
       </c>
       <c r="C197" s="3">
-        <v>5.7461199999999997E-2</v>
+        <v>5.7932400000000002E-2</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -2895,7 +2895,7 @@
         <v>18</v>
       </c>
       <c r="C198" s="3">
-        <v>5.55714E-2</v>
+        <v>5.6027100000000003E-2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -2906,7 +2906,7 @@
         <v>19</v>
       </c>
       <c r="C199" s="3">
-        <v>5.3848E-2</v>
+        <v>5.42896E-2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -2917,7 +2917,7 @@
         <v>20</v>
       </c>
       <c r="C200" s="3">
-        <v>5.2178799999999997E-2</v>
+        <v>5.2606699999999999E-2</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -2928,7 +2928,7 @@
         <v>21</v>
       </c>
       <c r="C201" s="3">
-        <v>5.05595E-2</v>
+        <v>5.0974100000000001E-2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -2939,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="C202" s="3">
-        <v>4.9087600000000002E-2</v>
+        <v>4.9490100000000002E-2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -2950,7 +2950,7 @@
         <v>10</v>
       </c>
       <c r="C203" s="3">
-        <v>4.7565099999999999E-2</v>
+        <v>4.7955100000000001E-2</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -2961,7 +2961,7 @@
         <v>11</v>
       </c>
       <c r="C204" s="3">
-        <v>4.6090199999999998E-2</v>
+        <v>4.6468099999999998E-2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -2972,7 +2972,7 @@
         <v>13</v>
       </c>
       <c r="C205" s="3">
-        <v>4.4106300000000001E-2</v>
+        <v>4.4468000000000001E-2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -2983,7 +2983,7 @@
         <v>14</v>
       </c>
       <c r="C206" s="3">
-        <v>4.2005199999999999E-2</v>
+        <v>4.2349600000000001E-2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -2994,7 +2994,7 @@
         <v>15</v>
       </c>
       <c r="C207" s="3">
-        <v>3.94416E-2</v>
+        <v>3.9765000000000002E-2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -3005,7 +3005,7 @@
         <v>16</v>
       </c>
       <c r="C208" s="3">
-        <v>3.7104400000000003E-2</v>
+        <v>3.7408700000000003E-2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -3016,7 +3016,7 @@
         <v>17</v>
       </c>
       <c r="C209" s="3">
-        <v>3.5003899999999998E-2</v>
+        <v>3.52909E-2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -3027,7 +3027,7 @@
         <v>18</v>
       </c>
       <c r="C210" s="3">
-        <v>3.3022500000000003E-2</v>
+        <v>3.3293299999999998E-2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -3038,7 +3038,7 @@
         <v>19</v>
       </c>
       <c r="C211" s="3">
-        <v>3.1153E-2</v>
+        <v>3.1408499999999999E-2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -3049,7 +3049,7 @@
         <v>20</v>
       </c>
       <c r="C212" s="3">
-        <v>2.9389999999999999E-2</v>
+        <v>2.9631000000000001E-2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -3060,7 +3060,7 @@
         <v>21</v>
       </c>
       <c r="C213" s="3">
-        <v>2.7778899999999999E-2</v>
+        <v>2.8006699999999999E-2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -3071,7 +3071,7 @@
         <v>9</v>
       </c>
       <c r="C214" s="3">
-        <v>2.62802E-2</v>
+        <v>2.6495700000000001E-2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -3082,7 +3082,7 @@
         <v>10</v>
       </c>
       <c r="C215" s="3">
-        <v>2.4864000000000001E-2</v>
+        <v>2.5067900000000001E-2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -3093,7 +3093,7 @@
         <v>11</v>
       </c>
       <c r="C216" s="3">
-        <v>2.3567600000000001E-2</v>
+        <v>2.3760900000000001E-2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -3104,7 +3104,7 @@
         <v>13</v>
       </c>
       <c r="C217" s="3">
-        <v>2.2402399999999999E-2</v>
+        <v>2.2586100000000001E-2</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -3115,7 +3115,7 @@
         <v>14</v>
       </c>
       <c r="C218" s="3">
-        <v>2.1335300000000001E-2</v>
+        <v>2.15102E-2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>15</v>
       </c>
       <c r="C219" s="3">
-        <v>2.03196E-2</v>
+        <v>2.04862E-2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -3137,7 +3137,7 @@
         <v>16</v>
       </c>
       <c r="C220" s="3">
-        <v>1.9351799999999999E-2</v>
+        <v>1.95105E-2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -3148,7 +3148,7 @@
         <v>17</v>
       </c>
       <c r="C221" s="3">
-        <v>1.83427E-2</v>
+        <v>1.8493099999999998E-2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -3159,7 +3159,7 @@
         <v>18</v>
       </c>
       <c r="C222" s="3">
-        <v>1.7386200000000001E-2</v>
+        <v>1.7528800000000001E-2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -3170,7 +3170,7 @@
         <v>19</v>
       </c>
       <c r="C223" s="3">
-        <v>1.6481099999999999E-2</v>
+        <v>1.6616200000000001E-2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -3181,7 +3181,7 @@
         <v>20</v>
       </c>
       <c r="C224" s="3">
-        <v>1.55479E-2</v>
+        <v>1.5675399999999999E-2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -3192,7 +3192,7 @@
         <v>21</v>
       </c>
       <c r="C225" s="3">
-        <v>1.45305E-2</v>
+        <v>1.46497E-2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -3203,7 +3203,7 @@
         <v>9</v>
       </c>
       <c r="C226" s="3">
-        <v>1.3579900000000001E-2</v>
+        <v>1.36913E-2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -3214,7 +3214,7 @@
         <v>10</v>
       </c>
       <c r="C227" s="3">
-        <v>1.26917E-2</v>
+        <v>1.27958E-2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -3225,7 +3225,7 @@
         <v>11</v>
       </c>
       <c r="C228" s="3">
-        <v>1.1917000000000001E-2</v>
+        <v>1.20147E-2</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
         <v>13</v>
       </c>
       <c r="C229" s="3">
-        <v>1.1189299999999999E-2</v>
+        <v>1.1281100000000001E-2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -3247,7 +3247,7 @@
         <v>14</v>
       </c>
       <c r="C230" s="3">
-        <v>1.0556100000000001E-2</v>
+        <v>1.06427E-2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -3258,7 +3258,7 @@
         <v>15</v>
       </c>
       <c r="C231" s="3">
-        <v>9.8934000000000001E-3</v>
+        <v>9.9745000000000007E-3</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -3269,7 +3269,7 @@
         <v>16</v>
       </c>
       <c r="C232" s="3">
-        <v>9.0766000000000006E-3</v>
+        <v>9.1509999999999994E-3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -3280,7 +3280,7 @@
         <v>17</v>
       </c>
       <c r="C233" s="3">
-        <v>8.3268000000000005E-3</v>
+        <v>8.3951000000000008E-3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -3291,7 +3291,7 @@
         <v>18</v>
       </c>
       <c r="C234" s="3">
-        <v>7.7102000000000004E-3</v>
+        <v>7.7733999999999998E-3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -3302,7 +3302,7 @@
         <v>19</v>
       </c>
       <c r="C235" s="3">
-        <v>7.1516000000000001E-3</v>
+        <v>7.2101999999999999E-3</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -3313,7 +3313,7 @@
         <v>20</v>
       </c>
       <c r="C236" s="3">
-        <v>6.5614999999999996E-3</v>
+        <v>6.6153000000000002E-3</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -3324,7 +3324,7 @@
         <v>21</v>
       </c>
       <c r="C237" s="3">
-        <v>6.0469E-3</v>
+        <v>6.0965000000000004E-3</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -3335,7 +3335,7 @@
         <v>9</v>
       </c>
       <c r="C238" s="3">
-        <v>5.5231000000000004E-3</v>
+        <v>5.5684000000000003E-3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -3346,7 +3346,7 @@
         <v>10</v>
       </c>
       <c r="C239" s="3">
-        <v>5.0343000000000002E-3</v>
+        <v>5.0756000000000004E-3</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -3357,7 +3357,7 @@
         <v>11</v>
       </c>
       <c r="C240" s="3">
-        <v>4.6442999999999996E-3</v>
+        <v>4.6823999999999998E-3</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -3368,7 +3368,7 @@
         <v>13</v>
       </c>
       <c r="C241" s="3">
-        <v>4.3160999999999998E-3</v>
+        <v>4.3515000000000003E-3</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -3379,7 +3379,7 @@
         <v>14</v>
       </c>
       <c r="C242" s="3">
-        <v>3.9309999999999996E-3</v>
+        <v>3.9632000000000001E-3</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -3390,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="C243" s="3">
-        <v>3.5013000000000002E-3</v>
+        <v>3.5300000000000002E-3</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -3401,7 +3401,7 @@
         <v>16</v>
       </c>
       <c r="C244" s="3">
-        <v>3.1828999999999998E-3</v>
+        <v>3.209E-3</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -3412,7 +3412,7 @@
         <v>17</v>
       </c>
       <c r="C245" s="3">
-        <v>2.9214000000000002E-3</v>
+        <v>2.9453999999999999E-3</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -3423,7 +3423,7 @@
         <v>18</v>
       </c>
       <c r="C246" s="3">
-        <v>2.6838000000000001E-3</v>
+        <v>2.7058E-3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -3434,7 +3434,7 @@
         <v>19</v>
       </c>
       <c r="C247" s="3">
-        <v>2.4575E-3</v>
+        <v>2.4777000000000002E-3</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -3445,7 +3445,7 @@
         <v>20</v>
       </c>
       <c r="C248" s="3">
-        <v>2.2279000000000001E-3</v>
+        <v>2.2461999999999998E-3</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -3456,7 +3456,7 @@
         <v>21</v>
       </c>
       <c r="C249" s="3">
-        <v>2.0138999999999999E-3</v>
+        <v>2.0303999999999999E-3</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -3467,7 +3467,7 @@
         <v>9</v>
       </c>
       <c r="C250" s="3">
-        <v>1.8228999999999999E-3</v>
+        <v>1.8377999999999999E-3</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -3478,7 +3478,7 @@
         <v>10</v>
       </c>
       <c r="C251" s="3">
-        <v>1.6182E-3</v>
+        <v>1.6314999999999999E-3</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -3489,7 +3489,7 @@
         <v>11</v>
       </c>
       <c r="C252" s="3">
-        <v>1.4732E-3</v>
+        <v>1.4852999999999999E-3</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -3500,7 +3500,7 @@
         <v>13</v>
       </c>
       <c r="C253" s="3">
-        <v>1.3332000000000001E-3</v>
+        <v>1.3441E-3</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -3511,7 +3511,7 @@
         <v>14</v>
       </c>
       <c r="C254" s="3">
-        <v>1.1842999999999999E-3</v>
+        <v>1.194E-3</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
         <v>15</v>
       </c>
       <c r="C255" s="3">
-        <v>1.0748999999999999E-3</v>
+        <v>1.0836999999999999E-3</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -3533,7 +3533,7 @@
         <v>16</v>
       </c>
       <c r="C256" s="3">
-        <v>9.5330000000000002E-4</v>
+        <v>9.611E-4</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>17</v>
       </c>
       <c r="C257" s="3">
-        <v>8.5300000000000003E-4</v>
+        <v>8.5999999999999998E-4</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -3555,7 +3555,7 @@
         <v>18</v>
       </c>
       <c r="C258" s="3">
-        <v>7.7499999999999997E-4</v>
+        <v>7.8140000000000002E-4</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -3566,7 +3566,7 @@
         <v>19</v>
       </c>
       <c r="C259" s="3">
-        <v>7.0969999999999996E-4</v>
+        <v>7.1549999999999999E-4</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -3577,7 +3577,7 @@
         <v>20</v>
       </c>
       <c r="C260" s="3">
-        <v>6.5959999999999999E-4</v>
+        <v>6.6500000000000001E-4</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -3588,7 +3588,7 @@
         <v>21</v>
       </c>
       <c r="C261" s="3">
-        <v>6.0899999999999995E-4</v>
+        <v>6.1399999999999996E-4</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -3599,7 +3599,7 @@
         <v>9</v>
       </c>
       <c r="C262" s="3">
-        <v>5.5860000000000003E-4</v>
+        <v>5.6320000000000003E-4</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -3610,7 +3610,7 @@
         <v>10</v>
       </c>
       <c r="C263" s="3">
-        <v>5.1239999999999999E-4</v>
+        <v>5.1659999999999998E-4</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -3621,7 +3621,7 @@
         <v>11</v>
       </c>
       <c r="C264" s="3">
-        <v>4.6050000000000003E-4</v>
+        <v>4.6430000000000001E-4</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -3632,7 +3632,7 @@
         <v>13</v>
       </c>
       <c r="C265" s="3">
-        <v>4.0709999999999997E-4</v>
+        <v>4.104E-4</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -3643,7 +3643,7 @@
         <v>14</v>
       </c>
       <c r="C266" s="3">
-        <v>3.4979999999999999E-4</v>
+        <v>3.5270000000000001E-4</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -3654,7 +3654,7 @@
         <v>15</v>
       </c>
       <c r="C267" s="3">
-        <v>0.30612879999999998</v>
+        <v>0.3086391</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -3665,7 +3665,7 @@
         <v>16</v>
       </c>
       <c r="C268" s="3">
-        <v>0.30647449999999998</v>
+        <v>0.30898759999999997</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -3676,7 +3676,7 @@
         <v>17</v>
       </c>
       <c r="C269" s="3">
-        <v>0.30409920000000001</v>
+        <v>0.3065928</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -3687,7 +3687,7 @@
         <v>18</v>
       </c>
       <c r="C270" s="3">
-        <v>0.29989969999999999</v>
+        <v>0.30235889999999999</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -3698,7 +3698,7 @@
         <v>19</v>
       </c>
       <c r="C271" s="3">
-        <v>0.29613729999999999</v>
+        <v>0.29856559999999999</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -3709,7 +3709,7 @@
         <v>20</v>
       </c>
       <c r="C272" s="3">
-        <v>0.29262549999999998</v>
+        <v>0.29502499999999998</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -3720,7 +3720,7 @@
         <v>21</v>
       </c>
       <c r="C273" s="3">
-        <v>0.28781600000000002</v>
+        <v>0.29017609999999999</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -3731,7 +3731,7 @@
         <v>9</v>
       </c>
       <c r="C274" s="3">
-        <v>0.28296500000000002</v>
+        <v>0.28528530000000002</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -3742,7 +3742,7 @@
         <v>10</v>
       </c>
       <c r="C275" s="3">
-        <v>0.27765840000000003</v>
+        <v>0.2799352</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -3753,7 +3753,7 @@
         <v>11</v>
       </c>
       <c r="C276" s="3">
-        <v>0.26883550000000001</v>
+        <v>0.27104</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
         <v>13</v>
       </c>
       <c r="C277" s="3">
-        <v>0.25061220000000001</v>
+        <v>0.25266719999999998</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -3775,7 +3775,7 @@
         <v>14</v>
       </c>
       <c r="C278" s="3">
-        <v>0.21453030000000001</v>
+        <v>0.21628939999999999</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -3786,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="C279" s="3">
-        <v>0.17935219999999999</v>
+        <v>0.18082290000000001</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -3797,7 +3797,7 @@
         <v>16</v>
       </c>
       <c r="C280" s="3">
-        <v>0.15661919999999999</v>
+        <v>0.1579035</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -3808,7 +3808,7 @@
         <v>17</v>
       </c>
       <c r="C281" s="3">
-        <v>0.1294804</v>
+        <v>0.13054209999999999</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -3819,7 +3819,7 @@
         <v>18</v>
       </c>
       <c r="C282" s="3">
-        <v>0.1048919</v>
+        <v>0.105752</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -3830,7 +3830,7 @@
         <v>19</v>
       </c>
       <c r="C283" s="3">
-        <v>8.8875300000000004E-2</v>
+        <v>8.9604100000000006E-2</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -3841,7 +3841,7 @@
         <v>20</v>
       </c>
       <c r="C284" s="3">
-        <v>8.6244399999999999E-2</v>
+        <v>8.6951600000000004E-2</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -3852,7 +3852,7 @@
         <v>21</v>
       </c>
       <c r="C285" s="3">
-        <v>8.1087900000000004E-2</v>
+        <v>8.17528E-2</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -3863,7 +3863,7 @@
         <v>9</v>
       </c>
       <c r="C286" s="3">
-        <v>7.6727299999999998E-2</v>
+        <v>7.7356499999999995E-2</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -3874,7 +3874,7 @@
         <v>10</v>
       </c>
       <c r="C287" s="3">
-        <v>7.0277900000000004E-2</v>
+        <v>7.0854200000000006E-2</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="C288" s="3">
-        <v>6.2281299999999998E-2</v>
+        <v>6.2792000000000001E-2</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -3896,7 +3896,7 @@
         <v>13</v>
       </c>
       <c r="C289" s="3">
-        <v>5.4564799999999997E-2</v>
+        <v>5.5012199999999997E-2</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -3907,7 +3907,7 @@
         <v>14</v>
       </c>
       <c r="C290" s="3">
-        <v>4.6832100000000002E-2</v>
+        <v>4.7216099999999997E-2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -3918,7 +3918,7 @@
         <v>15</v>
       </c>
       <c r="C291" s="3">
-        <v>3.9701699999999999E-2</v>
+        <v>4.0027300000000002E-2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -3929,7 +3929,7 @@
         <v>16</v>
       </c>
       <c r="C292" s="3">
-        <v>3.4222700000000002E-2</v>
+        <v>3.4503300000000001E-2</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -3940,7 +3940,7 @@
         <v>17</v>
       </c>
       <c r="C293" s="3">
-        <v>2.869E-2</v>
+        <v>2.8925300000000001E-2</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -3951,7 +3951,7 @@
         <v>18</v>
       </c>
       <c r="C294" s="3">
-        <v>2.4360199999999999E-2</v>
+        <v>2.4559999999999998E-2</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>19</v>
       </c>
       <c r="C295" s="3">
-        <v>2.0380100000000002E-2</v>
+        <v>2.0547200000000002E-2</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>20</v>
       </c>
       <c r="C296" s="3">
-        <v>1.6429699999999998E-2</v>
+        <v>1.65644E-2</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -3984,7 +3984,7 @@
         <v>21</v>
       </c>
       <c r="C297" s="3">
-        <v>1.3617000000000001E-2</v>
+        <v>1.37287E-2</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -3995,7 +3995,7 @@
         <v>9</v>
       </c>
       <c r="C298" s="3">
-        <v>1.09801E-2</v>
+        <v>1.1070099999999999E-2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -4006,7 +4006,7 @@
         <v>10</v>
       </c>
       <c r="C299" s="3">
-        <v>8.6294000000000006E-3</v>
+        <v>8.7001999999999999E-3</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -4017,7 +4017,7 @@
         <v>11</v>
       </c>
       <c r="C300" s="3">
-        <v>6.7989000000000001E-3</v>
+        <v>6.8547E-3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -4028,7 +4028,7 @@
         <v>13</v>
       </c>
       <c r="C301" s="3">
-        <v>5.2789460000000004</v>
+        <v>5.3222334</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -4039,7 +4039,7 @@
         <v>14</v>
       </c>
       <c r="C302" s="3">
-        <v>5.2789460000000004</v>
+        <v>5.3222334</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="C303" s="3">
-        <v>5.0955082999999997</v>
+        <v>5.1372914999999999</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -4061,7 +4061,7 @@
         <v>16</v>
       </c>
       <c r="C304" s="3">
-        <v>4.8029723000000004</v>
+        <v>4.8423566999999998</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -4072,7 +4072,7 @@
         <v>17</v>
       </c>
       <c r="C305" s="3">
-        <v>4.4759593000000004</v>
+        <v>4.5126622000000003</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -4083,7 +4083,7 @@
         <v>18</v>
       </c>
       <c r="C306" s="3">
-        <v>4.0713768999999997</v>
+        <v>4.1047621999999997</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,7 +4094,7 @@
         <v>19</v>
       </c>
       <c r="C307" s="3">
-        <v>3.2614274999999999</v>
+        <v>3.2881711999999998</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>20</v>
       </c>
       <c r="C308" s="3">
-        <v>2.5328406000000001</v>
+        <v>2.5536099000000001</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -4116,7 +4116,7 @@
         <v>21</v>
       </c>
       <c r="C309" s="3">
-        <v>1.9583564</v>
+        <v>1.9744149</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -4127,7 +4127,7 @@
         <v>9</v>
       </c>
       <c r="C310" s="3">
-        <v>1.4404851000000001</v>
+        <v>1.4522971</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,7 +4138,7 @@
         <v>10</v>
       </c>
       <c r="C311" s="3">
-        <v>1.0467044000000001</v>
+        <v>1.0552874000000001</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -4149,7 +4149,7 @@
         <v>11</v>
       </c>
       <c r="C312" s="3">
-        <v>0.74013549999999995</v>
+        <v>0.7462046</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,7 +4160,7 @@
         <v>13</v>
       </c>
       <c r="C313" s="3">
-        <v>0.48201630000000001</v>
+        <v>0.48596879999999998</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -4171,7 +4171,7 @@
         <v>14</v>
       </c>
       <c r="C314" s="3">
-        <v>0.3087685</v>
+        <v>0.31130039999999998</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>15</v>
       </c>
       <c r="C315" s="3">
-        <v>0.17870549999999999</v>
+        <v>0.18017089999999999</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,7 +4193,7 @@
         <v>16</v>
       </c>
       <c r="C316" s="3">
-        <v>0.1264904</v>
+        <v>0.12752759999999999</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,7 +4204,7 @@
         <v>17</v>
       </c>
       <c r="C317" s="3">
-        <v>0.1264904</v>
+        <v>0.12752759999999999</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,7 +4215,7 @@
         <v>18</v>
       </c>
       <c r="C318" s="3">
-        <v>0.1200334</v>
+        <v>0.12101770000000001</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -4226,7 +4226,7 @@
         <v>19</v>
       </c>
       <c r="C319" s="3">
-        <v>0.10950840000000001</v>
+        <v>0.1104064</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -4237,7 +4237,7 @@
         <v>20</v>
       </c>
       <c r="C320" s="3">
-        <v>9.8843899999999998E-2</v>
+        <v>9.9654400000000004E-2</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -4248,7 +4248,7 @@
         <v>21</v>
       </c>
       <c r="C321" s="3">
-        <v>8.9386400000000005E-2</v>
+        <v>9.0119400000000002E-2</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -4259,7 +4259,7 @@
         <v>9</v>
       </c>
       <c r="C322" s="3">
-        <v>7.9208100000000004E-2</v>
+        <v>7.9857600000000001E-2</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -4270,7 +4270,7 @@
         <v>10</v>
       </c>
       <c r="C323" s="3">
-        <v>6.9657700000000003E-2</v>
+        <v>7.0228899999999997E-2</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -4281,7 +4281,7 @@
         <v>11</v>
       </c>
       <c r="C324" s="3">
-        <v>5.9720799999999997E-2</v>
+        <v>6.02105E-2</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -4292,7 +4292,7 @@
         <v>13</v>
       </c>
       <c r="C325" s="3">
-        <v>5.0022200000000003E-2</v>
+        <v>5.0432400000000002E-2</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -4303,7 +4303,7 @@
         <v>14</v>
       </c>
       <c r="C326" s="3">
-        <v>4.1611799999999997E-2</v>
+        <v>4.1952999999999997E-2</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -4314,7 +4314,7 @@
         <v>15</v>
       </c>
       <c r="C327" s="3">
-        <v>3.88895E-2</v>
+        <v>3.9208399999999997E-2</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -4325,7 +4325,7 @@
         <v>16</v>
       </c>
       <c r="C328" s="3">
-        <v>3.5843199999999999E-2</v>
+        <v>3.6137099999999998E-2</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -4336,7 +4336,7 @@
         <v>17</v>
       </c>
       <c r="C329" s="3">
-        <v>3.29044E-2</v>
+        <v>3.3174200000000001E-2</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -4347,7 +4347,7 @@
         <v>18</v>
       </c>
       <c r="C330" s="3">
-        <v>3.01903E-2</v>
+        <v>3.04379E-2</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -4358,7 +4358,7 @@
         <v>19</v>
       </c>
       <c r="C331" s="3">
-        <v>2.7596599999999999E-2</v>
+        <v>2.7822900000000001E-2</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -4369,7 +4369,7 @@
         <v>20</v>
       </c>
       <c r="C332" s="3">
-        <v>2.50762E-2</v>
+        <v>2.52818E-2</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="C333" s="3">
-        <v>2.24E-2</v>
+        <v>2.2583700000000002E-2</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -4391,7 +4391,7 @@
         <v>9</v>
       </c>
       <c r="C334" s="3">
-        <v>1.9180599999999999E-2</v>
+        <v>1.9337900000000002E-2</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -4402,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="C335" s="3">
-        <v>1.60152E-2</v>
+        <v>1.6146500000000001E-2</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>11</v>
       </c>
       <c r="C336" s="3">
-        <v>1.22703E-2</v>
+        <v>1.2370900000000001E-2</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -4424,7 +4424,7 @@
         <v>13</v>
       </c>
       <c r="C337" s="3">
-        <v>9.5548000000000004E-3</v>
+        <v>9.6331000000000003E-3</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -4435,7 +4435,7 @@
         <v>14</v>
       </c>
       <c r="C338" s="3">
-        <v>7.6146E-3</v>
+        <v>7.6769999999999998E-3</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -4446,7 +4446,7 @@
         <v>15</v>
       </c>
       <c r="C339" s="3">
-        <v>6.0619000000000003E-3</v>
+        <v>6.1116E-3</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -4457,7 +4457,7 @@
         <v>16</v>
       </c>
       <c r="C340" s="3">
-        <v>4.8776000000000002E-3</v>
+        <v>4.9176000000000003E-3</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -4468,7 +4468,7 @@
         <v>17</v>
       </c>
       <c r="C341" s="3">
-        <v>4.0293000000000004E-3</v>
+        <v>4.0622999999999996E-3</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -4479,7 +4479,7 @@
         <v>18</v>
       </c>
       <c r="C342" s="3">
-        <v>3.3630000000000001E-3</v>
+        <v>3.3906000000000001E-3</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -4490,7 +4490,7 @@
         <v>19</v>
       </c>
       <c r="C343" s="3">
-        <v>2.7782000000000002E-3</v>
+        <v>2.8010000000000001E-3</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -4501,7 +4501,7 @@
         <v>20</v>
       </c>
       <c r="C344" s="3">
-        <v>2.2464E-3</v>
+        <v>2.2648E-3</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -4512,7 +4512,7 @@
         <v>21</v>
       </c>
       <c r="C345" s="3">
-        <v>1.8226E-3</v>
+        <v>1.8374999999999999E-3</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -4523,7 +4523,7 @@
         <v>9</v>
       </c>
       <c r="C346" s="3">
-        <v>1.4538000000000001E-3</v>
+        <v>1.4656999999999999E-3</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -4534,7 +4534,7 @@
         <v>10</v>
       </c>
       <c r="C347" s="3">
-        <v>1.1620999999999999E-3</v>
+        <v>1.1716000000000001E-3</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -4545,7 +4545,7 @@
         <v>11</v>
       </c>
       <c r="C348" s="3">
-        <v>9.4280000000000004E-4</v>
+        <v>9.5049999999999996E-4</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -4556,7 +4556,7 @@
         <v>13</v>
       </c>
       <c r="C349" s="3">
-        <v>7.6040000000000005E-4</v>
+        <v>7.6659999999999999E-4</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -4567,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="C350" s="3">
-        <v>5.9980000000000005E-4</v>
+        <v>6.0470000000000001E-4</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -4578,7 +4578,7 @@
         <v>15</v>
       </c>
       <c r="C351" s="3">
-        <v>4.7409999999999998E-4</v>
+        <v>4.7800000000000002E-4</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <v>16</v>
       </c>
       <c r="C352" s="3">
-        <v>3.7790000000000002E-4</v>
+        <v>3.8099999999999999E-4</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,7 +4600,7 @@
         <v>17</v>
       </c>
       <c r="C353" s="3">
-        <v>2.9379999999999999E-4</v>
+        <v>2.9619999999999999E-4</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,7 +4611,7 @@
         <v>18</v>
       </c>
       <c r="C354" s="3">
-        <v>2.288E-4</v>
+        <v>2.307E-4</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,7 +4622,7 @@
         <v>19</v>
       </c>
       <c r="C355" s="3">
-        <v>1.7589999999999999E-4</v>
+        <v>1.773E-4</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,7 +4633,7 @@
         <v>20</v>
       </c>
       <c r="C356" s="3">
-        <v>0.13484779999999999</v>
+        <v>0.13595360000000001</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,7 +4644,7 @@
         <v>21</v>
       </c>
       <c r="C357" s="3">
-        <v>0.10112989999999999</v>
+        <v>0.1019592</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,7 +4655,7 @@
         <v>9</v>
       </c>
       <c r="C358" s="3">
-        <v>7.5123200000000001E-2</v>
+        <v>7.5739200000000007E-2</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,7 +4666,7 @@
         <v>10</v>
       </c>
       <c r="C359" s="3">
-        <v>5.5023000000000002E-2</v>
+        <v>5.5474200000000001E-2</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -4677,7 +4677,7 @@
         <v>11</v>
       </c>
       <c r="C360" s="3">
-        <v>4.0410799999999997E-2</v>
+        <v>4.0742199999999999E-2</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -4688,7 +4688,7 @@
         <v>13</v>
       </c>
       <c r="C361" s="3">
-        <v>2.954E-2</v>
+        <v>2.9782200000000002E-2</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -4699,7 +4699,7 @@
         <v>14</v>
       </c>
       <c r="C362" s="3">
-        <v>2.08851E-2</v>
+        <v>2.1056399999999999E-2</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -4710,7 +4710,7 @@
         <v>15</v>
       </c>
       <c r="C363" s="3">
-        <v>1.4932300000000001E-2</v>
+        <v>1.5054700000000001E-2</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -4721,7 +4721,7 @@
         <v>16</v>
       </c>
       <c r="C364" s="3">
-        <v>1.0527E-2</v>
+        <v>1.0613300000000001E-2</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -4732,7 +4732,7 @@
         <v>17</v>
       </c>
       <c r="C365" s="3">
-        <v>7.2113999999999998E-3</v>
+        <v>7.2705000000000001E-3</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -4743,7 +4743,7 @@
         <v>18</v>
       </c>
       <c r="C366" s="3">
-        <v>4.9246999999999997E-3</v>
+        <v>4.9651000000000001E-3</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="C367" s="3">
-        <v>9.2209380000000003</v>
+        <v>9.2965496999999999</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,7 +4765,7 @@
         <v>20</v>
       </c>
       <c r="C368" s="3">
-        <v>8.6924384000000003</v>
+        <v>8.7637163999999999</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -4776,7 +4776,7 @@
         <v>21</v>
       </c>
       <c r="C369" s="3">
-        <v>8.2424026999999995</v>
+        <v>8.3099904000000002</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>9</v>
       </c>
       <c r="C370" s="3">
-        <v>8.1197932000000002</v>
+        <v>8.1863755000000005</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>10</v>
       </c>
       <c r="C371" s="3">
-        <v>7.9715232</v>
+        <v>8.0368896999999997</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -4809,7 +4809,7 @@
         <v>11</v>
       </c>
       <c r="C372" s="3">
-        <v>7.7191082</v>
+        <v>7.7824049000000004</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -4820,7 +4820,7 @@
         <v>13</v>
       </c>
       <c r="C373" s="3">
-        <v>7.5536824999999999</v>
+        <v>7.6156227000000003</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -4831,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="C374" s="3">
-        <v>7.4296085999999999</v>
+        <v>7.4905314000000001</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -4842,7 +4842,7 @@
         <v>15</v>
       </c>
       <c r="C375" s="3">
-        <v>7.3567761999999997</v>
+        <v>7.4171018000000002</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>16</v>
       </c>
       <c r="C376" s="3">
-        <v>7.2544884999999999</v>
+        <v>7.3139753000000001</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -4864,7 +4864,7 @@
         <v>17</v>
       </c>
       <c r="C377" s="3">
-        <v>7.1178255999999998</v>
+        <v>7.1761917999999998</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -4875,7 +4875,7 @@
         <v>18</v>
       </c>
       <c r="C378" s="3">
-        <v>6.9394806999999998</v>
+        <v>6.9963844000000002</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -4886,7 +4886,7 @@
         <v>19</v>
       </c>
       <c r="C379" s="3">
-        <v>6.8154399000000003</v>
+        <v>6.8713265000000003</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -4897,7 +4897,7 @@
         <v>20</v>
       </c>
       <c r="C380" s="3">
-        <v>6.6518046000000002</v>
+        <v>6.7063493999999997</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -4908,7 +4908,7 @@
         <v>21</v>
       </c>
       <c r="C381" s="3">
-        <v>6.5846419999999997</v>
+        <v>6.6386361000000003</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -4919,7 +4919,7 @@
         <v>9</v>
       </c>
       <c r="C382" s="3">
-        <v>6.5084923000000003</v>
+        <v>6.5618619000000002</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -4930,7 +4930,7 @@
         <v>10</v>
       </c>
       <c r="C383" s="3">
-        <v>6.4186325000000002</v>
+        <v>6.4712652999999998</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>11</v>
       </c>
       <c r="C384" s="3">
-        <v>6.3231523999999997</v>
+        <v>6.3750022</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -4952,7 +4952,7 @@
         <v>13</v>
       </c>
       <c r="C385" s="3">
-        <v>6.2205133999999997</v>
+        <v>6.2715215999999998</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -4963,7 +4963,7 @@
         <v>14</v>
       </c>
       <c r="C386" s="3">
-        <v>6.1310010999999998</v>
+        <v>6.1812753000000003</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -4974,7 +4974,7 @@
         <v>15</v>
       </c>
       <c r="C387" s="3">
-        <v>6.0877777000000002</v>
+        <v>6.1376974999999998</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -4985,7 +4985,7 @@
         <v>16</v>
       </c>
       <c r="C388" s="3">
-        <v>6.0701744</v>
+        <v>6.1199497999999997</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -4996,7 +4996,7 @@
         <v>17</v>
       </c>
       <c r="C389" s="3">
-        <v>6.0142423999999997</v>
+        <v>6.0635592000000003</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -5007,7 +5007,7 @@
         <v>18</v>
       </c>
       <c r="C390" s="3">
-        <v>5.9382327000000004</v>
+        <v>5.9869262000000001</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -5018,7 +5018,7 @@
         <v>19</v>
       </c>
       <c r="C391" s="3">
-        <v>5.8602908999999999</v>
+        <v>5.9083452999999997</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
@@ -5029,7 +5029,7 @@
         <v>20</v>
       </c>
       <c r="C392" s="3">
-        <v>5.7908016</v>
+        <v>5.8382861999999998</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
         <v>21</v>
       </c>
       <c r="C393" s="3">
-        <v>5.7619916</v>
+        <v>5.8092398999999997</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -5051,7 +5051,7 @@
         <v>9</v>
       </c>
       <c r="C394" s="3">
-        <v>5.7608385999999996</v>
+        <v>5.8080774999999996</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -5062,7 +5062,7 @@
         <v>10</v>
       </c>
       <c r="C395" s="3">
-        <v>5.7390312999999997</v>
+        <v>5.7860914000000001</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -5073,7 +5073,7 @@
         <v>11</v>
       </c>
       <c r="C396" s="3">
-        <v>5.7195840000000002</v>
+        <v>5.7664846000000001</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -5084,7 +5084,7 @@
         <v>13</v>
       </c>
       <c r="C397" s="3">
-        <v>5.7007713000000004</v>
+        <v>5.7475176000000001</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -5095,7 +5095,7 @@
         <v>14</v>
       </c>
       <c r="C398" s="3">
-        <v>5.6549661999999996</v>
+        <v>5.7013369000000003</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -5106,7 +5106,7 @@
         <v>15</v>
       </c>
       <c r="C399" s="3">
-        <v>5.6296331000000004</v>
+        <v>5.6757961000000003</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -5117,7 +5117,7 @@
         <v>16</v>
       </c>
       <c r="C400" s="3">
-        <v>5.5916098999999999</v>
+        <v>5.6374611000000003</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -5128,7 +5128,7 @@
         <v>17</v>
       </c>
       <c r="C401" s="3">
-        <v>5.5582601</v>
+        <v>5.6038378</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -5139,7 +5139,7 @@
         <v>18</v>
       </c>
       <c r="C402" s="3">
-        <v>5.5521526000000003</v>
+        <v>5.5976803000000004</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -5150,7 +5150,7 @@
         <v>19</v>
       </c>
       <c r="C403" s="3">
-        <v>5.5327887000000002</v>
+        <v>5.5781575999999999</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -5161,7 +5161,7 @@
         <v>20</v>
       </c>
       <c r="C404" s="3">
-        <v>5.5228469000000002</v>
+        <v>5.5681342000000003</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -5172,7 +5172,7 @@
         <v>21</v>
       </c>
       <c r="C405" s="3">
-        <v>5.5245055000000001</v>
+        <v>5.5698064</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -5183,7 +5183,7 @@
         <v>9</v>
       </c>
       <c r="C406" s="3">
-        <v>5.5189852999999998</v>
+        <v>5.564241</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -5194,7 +5194,7 @@
         <v>10</v>
       </c>
       <c r="C407" s="3">
-        <v>5.5030266000000001</v>
+        <v>5.5481514000000001</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -5205,7 +5205,7 @@
         <v>11</v>
       </c>
       <c r="C408" s="3">
-        <v>5.4947847000000003</v>
+        <v>5.5398418999999999</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>13</v>
       </c>
       <c r="C409" s="3">
-        <v>5.4636415999999999</v>
+        <v>5.5084435000000003</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -5227,7 +5227,7 @@
         <v>14</v>
       </c>
       <c r="C410" s="3">
-        <v>5.4175928000000004</v>
+        <v>5.4620170999999997</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -5238,7 +5238,7 @@
         <v>15</v>
       </c>
       <c r="C411" s="3">
-        <v>5.3884943999999999</v>
+        <v>5.4326800999999998</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -5249,7 +5249,7 @@
         <v>16</v>
       </c>
       <c r="C412" s="3">
-        <v>5.3622196000000004</v>
+        <v>5.4061897999999999</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -5260,7 +5260,7 @@
         <v>17</v>
       </c>
       <c r="C413" s="3">
-        <v>5.3381974999999997</v>
+        <v>5.3819707000000001</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -5271,7 +5271,7 @@
         <v>18</v>
       </c>
       <c r="C414" s="3">
-        <v>5.3000376999999999</v>
+        <v>5.3434980000000003</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -5282,7 +5282,7 @@
         <v>19</v>
       </c>
       <c r="C415" s="3">
-        <v>5.2920993000000003</v>
+        <v>5.3354945000000003</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -5293,7 +5293,7 @@
         <v>20</v>
       </c>
       <c r="C416" s="3">
-        <v>5.3069582999999998</v>
+        <v>5.3504753999999997</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -5304,7 +5304,7 @@
         <v>21</v>
       </c>
       <c r="C417" s="3">
-        <v>5.3330907999999999</v>
+        <v>5.3768221</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -5315,7 +5315,7 @@
         <v>9</v>
       </c>
       <c r="C418" s="3">
-        <v>5.3496747999999998</v>
+        <v>5.3935421000000003</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -5326,7 +5326,7 @@
         <v>10</v>
       </c>
       <c r="C419" s="3">
-        <v>5.3437960999999996</v>
+        <v>5.3876151999999999</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -5337,7 +5337,7 @@
         <v>11</v>
       </c>
       <c r="C420" s="3">
-        <v>5.3534319000000004</v>
+        <v>5.3973300000000002</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -5348,7 +5348,7 @@
         <v>13</v>
       </c>
       <c r="C421" s="3">
-        <v>5.3310426</v>
+        <v>5.3747571000000001</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -5359,7 +5359,7 @@
         <v>14</v>
       </c>
       <c r="C422" s="3">
-        <v>5.2966141999999996</v>
+        <v>5.3400464000000003</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -5370,7 +5370,7 @@
         <v>15</v>
       </c>
       <c r="C423" s="3">
-        <v>5.2291581000000003</v>
+        <v>5.2720371999999998</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -5381,7 +5381,7 @@
         <v>16</v>
       </c>
       <c r="C424" s="3">
-        <v>5.1630700999999997</v>
+        <v>5.2054073000000001</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -5392,7 +5392,7 @@
         <v>17</v>
       </c>
       <c r="C425" s="3">
-        <v>5.1389174999999998</v>
+        <v>5.1810565999999998</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -5403,7 +5403,7 @@
         <v>18</v>
       </c>
       <c r="C426" s="3">
-        <v>5.1363491999999997</v>
+        <v>5.1784673000000003</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -5414,7 +5414,7 @@
         <v>19</v>
       </c>
       <c r="C427" s="3">
-        <v>5.1327568000000001</v>
+        <v>5.1748453999999997</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>20</v>
       </c>
       <c r="C428" s="3">
-        <v>5.0950530000000001</v>
+        <v>5.1368324000000003</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -5436,7 +5436,7 @@
         <v>21</v>
       </c>
       <c r="C429" s="3">
-        <v>5.0671832999999999</v>
+        <v>5.1087341999999998</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -5447,7 +5447,7 @@
         <v>9</v>
       </c>
       <c r="C430" s="3">
-        <v>5.047498</v>
+        <v>5.0888875000000002</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -5458,7 +5458,7 @@
         <v>10</v>
       </c>
       <c r="C431" s="3">
-        <v>4.9995032999999998</v>
+        <v>5.0404992000000002</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -5469,7 +5469,7 @@
         <v>11</v>
       </c>
       <c r="C432" s="3">
-        <v>4.9529453999999999</v>
+        <v>4.9935596000000002</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -5480,7 +5480,7 @@
         <v>13</v>
       </c>
       <c r="C433" s="3">
-        <v>4.9165622999999998</v>
+        <v>4.9568781</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -5491,7 +5491,7 @@
         <v>14</v>
       </c>
       <c r="C434" s="3">
-        <v>4.8867535000000002</v>
+        <v>4.9268248999999997</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -5502,7 +5502,7 @@
         <v>15</v>
       </c>
       <c r="C435" s="3">
-        <v>4.8843117999999999</v>
+        <v>4.9243632000000002</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -5513,7 +5513,7 @@
         <v>16</v>
       </c>
       <c r="C436" s="3">
-        <v>4.8779702</v>
+        <v>4.9179696000000002</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -5524,7 +5524,7 @@
         <v>17</v>
       </c>
       <c r="C437" s="3">
-        <v>4.8735844000000004</v>
+        <v>4.9135477999999999</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -5535,7 +5535,7 @@
         <v>18</v>
       </c>
       <c r="C438" s="3">
-        <v>4.8760215999999996</v>
+        <v>4.9160050000000002</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -5546,7 +5546,7 @@
         <v>19</v>
       </c>
       <c r="C439" s="3">
-        <v>4.8614373000000004</v>
+        <v>4.9013011000000004</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -5557,7 +5557,7 @@
         <v>20</v>
       </c>
       <c r="C440" s="3">
-        <v>4.7947899999999999</v>
+        <v>4.8341073000000003</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -5568,7 +5568,7 @@
         <v>21</v>
       </c>
       <c r="C441" s="3">
-        <v>4.7374672999999996</v>
+        <v>4.7763144999999998</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -5579,7 +5579,7 @@
         <v>9</v>
       </c>
       <c r="C442" s="3">
-        <v>4.7171827000000004</v>
+        <v>4.7558635999999996</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -5590,7 +5590,7 @@
         <v>10</v>
       </c>
       <c r="C443" s="3">
-        <v>4.7096477999999999</v>
+        <v>4.7482669</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -5601,7 +5601,7 @@
         <v>11</v>
       </c>
       <c r="C444" s="3">
-        <v>4.6960287000000003</v>
+        <v>4.7345360999999997</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -5612,7 +5612,7 @@
         <v>13</v>
       </c>
       <c r="C445" s="3">
-        <v>4.6703410999999999</v>
+        <v>4.7086379000000003</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -5623,7 +5623,7 @@
         <v>14</v>
       </c>
       <c r="C446" s="3">
-        <v>4.6346556000000003</v>
+        <v>4.6726597999999999</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -5634,7 +5634,7 @@
         <v>15</v>
       </c>
       <c r="C447" s="3">
-        <v>4.6120555000000003</v>
+        <v>4.6498743999999999</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -5645,7 +5645,7 @@
         <v>16</v>
       </c>
       <c r="C448" s="3">
-        <v>4.5900236000000003</v>
+        <v>4.6276618000000003</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -5656,7 +5656,7 @@
         <v>17</v>
       </c>
       <c r="C449" s="3">
-        <v>4.5517887999999997</v>
+        <v>4.5891134999999998</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -5667,7 +5667,7 @@
         <v>18</v>
       </c>
       <c r="C450" s="3">
-        <v>4.5259904999999998</v>
+        <v>4.5631035999999998</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -5678,7 +5678,7 @@
         <v>19</v>
       </c>
       <c r="C451" s="3">
-        <v>4.4989965999999999</v>
+        <v>4.5358884000000002</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -5689,7 +5689,7 @@
         <v>20</v>
       </c>
       <c r="C452" s="3">
-        <v>4.4496057000000002</v>
+        <v>4.4860924999999998</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -5700,7 +5700,7 @@
         <v>21</v>
       </c>
       <c r="C453" s="3">
-        <v>4.4147296000000003</v>
+        <v>4.4509303999999998</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -5711,7 +5711,7 @@
         <v>9</v>
       </c>
       <c r="C454" s="3">
-        <v>4.3953895000000003</v>
+        <v>4.4314317000000001</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -5722,7 +5722,7 @@
         <v>10</v>
       </c>
       <c r="C455" s="3">
-        <v>4.3544581000000004</v>
+        <v>4.3901646999999997</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -5733,7 +5733,7 @@
         <v>11</v>
       </c>
       <c r="C456" s="3">
-        <v>4.2990009999999996</v>
+        <v>4.3342527999999998</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -5744,7 +5744,7 @@
         <v>13</v>
       </c>
       <c r="C457" s="3">
-        <v>4.2674218000000002</v>
+        <v>4.3024146999999999</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -5755,7 +5755,7 @@
         <v>14</v>
       </c>
       <c r="C458" s="3">
-        <v>4.2222441000000002</v>
+        <v>4.2568665000000001</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -5766,7 +5766,7 @@
         <v>15</v>
       </c>
       <c r="C459" s="3">
-        <v>4.2091954999999999</v>
+        <v>4.2437109</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -5777,7 +5777,7 @@
         <v>16</v>
       </c>
       <c r="C460" s="3">
-        <v>4.1832583999999997</v>
+        <v>4.2175611000000002</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -5788,7 +5788,7 @@
         <v>17</v>
       </c>
       <c r="C461" s="3">
-        <v>4.1550053</v>
+        <v>4.1890763</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -5799,7 +5799,7 @@
         <v>18</v>
       </c>
       <c r="C462" s="3">
-        <v>4.1512685999999999</v>
+        <v>4.1853090000000002</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -5810,7 +5810,7 @@
         <v>19</v>
       </c>
       <c r="C463" s="3">
-        <v>4.1260998999999998</v>
+        <v>4.1599339000000004</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -5821,7 +5821,7 @@
         <v>20</v>
       </c>
       <c r="C464" s="3">
-        <v>4.0791896999999997</v>
+        <v>4.1126391</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -5832,7 +5832,7 @@
         <v>21</v>
       </c>
       <c r="C465" s="3">
-        <v>4.0444072999999996</v>
+        <v>4.0775714000000001</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -5843,7 +5843,7 @@
         <v>9</v>
       </c>
       <c r="C466" s="3">
-        <v>4.0111154000000004</v>
+        <v>4.0440065000000001</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -5854,7 +5854,7 @@
         <v>10</v>
       </c>
       <c r="C467" s="3">
-        <v>3.9491144</v>
+        <v>3.9814970999999999</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -5865,7 +5865,7 @@
         <v>11</v>
       </c>
       <c r="C468" s="3">
-        <v>3.8196287</v>
+        <v>3.8509497000000001</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -5876,7 +5876,7 @@
         <v>13</v>
       </c>
       <c r="C469" s="3">
-        <v>3.7192105</v>
+        <v>3.749708</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -5887,7 +5887,7 @@
         <v>14</v>
       </c>
       <c r="C470" s="3">
-        <v>3.6295598</v>
+        <v>3.6593222000000001</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -5898,7 +5898,7 @@
         <v>15</v>
       </c>
       <c r="C471" s="3">
-        <v>3.5773312000000002</v>
+        <v>3.6066653</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -5909,7 +5909,7 @@
         <v>16</v>
       </c>
       <c r="C472" s="3">
-        <v>3.5289836999999999</v>
+        <v>3.5579214000000001</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
@@ -5920,7 +5920,7 @@
         <v>17</v>
       </c>
       <c r="C473" s="3">
-        <v>3.4809461000000002</v>
+        <v>3.5094899000000002</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -5931,7 +5931,7 @@
         <v>18</v>
       </c>
       <c r="C474" s="3">
-        <v>3.4468228999999999</v>
+        <v>3.4750868000000001</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -5942,7 +5942,7 @@
         <v>19</v>
       </c>
       <c r="C475" s="3">
-        <v>3.4488922</v>
+        <v>3.4771730999999999</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>20</v>
       </c>
       <c r="C476" s="3">
-        <v>3.4475131999999999</v>
+        <v>3.4757828000000002</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -5964,7 +5964,7 @@
         <v>21</v>
       </c>
       <c r="C477" s="3">
-        <v>3.4413184000000001</v>
+        <v>3.4695372</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -5975,7 +5975,7 @@
         <v>9</v>
       </c>
       <c r="C478" s="3">
-        <v>3.4133300000000002</v>
+        <v>3.4413193</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -5986,7 +5986,7 @@
         <v>10</v>
       </c>
       <c r="C479" s="3">
-        <v>3.4000691000000001</v>
+        <v>3.4279497000000001</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -5997,7 +5997,7 @@
         <v>11</v>
       </c>
       <c r="C480" s="3">
-        <v>3.3875350000000002</v>
+        <v>3.4153128000000001</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -6008,7 +6008,7 @@
         <v>13</v>
       </c>
       <c r="C481" s="3">
-        <v>3.3693412999999999</v>
+        <v>3.3969699000000002</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -6019,7 +6019,7 @@
         <v>14</v>
       </c>
       <c r="C482" s="3">
-        <v>3.3416054000000002</v>
+        <v>3.3690066000000001</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -6030,7 +6030,7 @@
         <v>15</v>
       </c>
       <c r="C483" s="3">
-        <v>3.3286243999999998</v>
+        <v>3.3559190999999999</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -6041,7 +6041,7 @@
         <v>16</v>
       </c>
       <c r="C484" s="3">
-        <v>3.3097580999999998</v>
+        <v>3.3368981</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -6052,7 +6052,7 @@
         <v>17</v>
       </c>
       <c r="C485" s="3">
-        <v>3.2962435000000001</v>
+        <v>3.3232727</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -6063,7 +6063,7 @@
         <v>18</v>
       </c>
       <c r="C486" s="3">
-        <v>3.2831112999999998</v>
+        <v>3.3100328000000001</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -6074,7 +6074,7 @@
         <v>19</v>
       </c>
       <c r="C487" s="3">
-        <v>3.266778</v>
+        <v>3.2935656</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -6085,7 +6085,7 @@
         <v>20</v>
       </c>
       <c r="C488" s="3">
-        <v>3.2431028999999998</v>
+        <v>3.2696963000000001</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -6096,7 +6096,7 @@
         <v>21</v>
       </c>
       <c r="C489" s="3">
-        <v>3.2269684999999999</v>
+        <v>3.2534296</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -6107,7 +6107,7 @@
         <v>9</v>
       </c>
       <c r="C490" s="3">
-        <v>3.2214925999999999</v>
+        <v>3.2479087999999998</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -6118,7 +6118,7 @@
         <v>10</v>
       </c>
       <c r="C491" s="3">
-        <v>3.2160242999999999</v>
+        <v>3.2423956999999999</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -6129,7 +6129,7 @@
         <v>11</v>
       </c>
       <c r="C492" s="3">
-        <v>3.2019359000000001</v>
+        <v>3.2281917999999998</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -6140,7 +6140,7 @@
         <v>13</v>
       </c>
       <c r="C493" s="3">
-        <v>3.1746346999999999</v>
+        <v>3.2006667000000002</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
         <v>14</v>
       </c>
       <c r="C494" s="3">
-        <v>3.1566409000000002</v>
+        <v>3.1825253999999998</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -6162,7 +6162,7 @@
         <v>15</v>
       </c>
       <c r="C495" s="3">
-        <v>3.1428124</v>
+        <v>3.1685835</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -6173,7 +6173,7 @@
         <v>16</v>
       </c>
       <c r="C496" s="3">
-        <v>3.1200367</v>
+        <v>3.1456209999999998</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -6184,7 +6184,7 @@
         <v>17</v>
       </c>
       <c r="C497" s="3">
-        <v>3.0919002999999998</v>
+        <v>3.1172539000000001</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -6195,7 +6195,7 @@
         <v>18</v>
       </c>
       <c r="C498" s="3">
-        <v>3.0704077000000001</v>
+        <v>3.0955849999999998</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -6206,7 +6206,7 @@
         <v>19</v>
       </c>
       <c r="C499" s="3">
-        <v>3.0737880999999998</v>
+        <v>3.0989931999999998</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -6217,7 +6217,7 @@
         <v>20</v>
       </c>
       <c r="C500" s="3">
-        <v>3.0728669000000002</v>
+        <v>3.0980644000000002</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -6228,7 +6228,7 @@
         <v>21</v>
       </c>
       <c r="C501" s="3">
-        <v>3.0728669000000002</v>
+        <v>3.0980644000000002</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -6239,7 +6239,7 @@
         <v>9</v>
       </c>
       <c r="C502" s="3">
-        <v>3.0682643999999999</v>
+        <v>3.0934241999999998</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -6250,7 +6250,7 @@
         <v>10</v>
       </c>
       <c r="C503" s="3">
-        <v>3.0505705000000001</v>
+        <v>3.0755851999999999</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -6261,7 +6261,7 @@
         <v>11</v>
       </c>
       <c r="C504" s="3">
-        <v>3.0341866</v>
+        <v>3.0590668999999999</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -6272,7 +6272,7 @@
         <v>13</v>
       </c>
       <c r="C505" s="3">
-        <v>3.0220975999999999</v>
+        <v>3.0468788</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -6283,7 +6283,7 @@
         <v>14</v>
       </c>
       <c r="C506" s="3">
-        <v>3.0106582</v>
+        <v>3.0353455999999999</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -6294,7 +6294,7 @@
         <v>15</v>
       </c>
       <c r="C507" s="3">
-        <v>3.0037487</v>
+        <v>3.0283793999999999</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -6305,7 +6305,7 @@
         <v>16</v>
       </c>
       <c r="C508" s="3">
-        <v>2.9956610000000001</v>
+        <v>3.0202254000000002</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -6316,7 +6316,7 @@
         <v>17</v>
       </c>
       <c r="C509" s="3">
-        <v>2.9920705000000001</v>
+        <v>3.0166054999999998</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -6327,7 +6327,7 @@
         <v>18</v>
       </c>
       <c r="C510" s="3">
-        <v>2.9881855000000002</v>
+        <v>3.0126886000000002</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -6338,7 +6338,7 @@
         <v>19</v>
       </c>
       <c r="C511" s="3">
-        <v>2.9902790000000001</v>
+        <v>3.0147993</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -6349,7 +6349,7 @@
         <v>20</v>
       </c>
       <c r="C512" s="3">
-        <v>2.9869933</v>
+        <v>3.0114866</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -6360,7 +6360,7 @@
         <v>21</v>
       </c>
       <c r="C513" s="3">
-        <v>2.9875905999999999</v>
+        <v>3.0120887999999999</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -6371,7 +6371,7 @@
         <v>9</v>
       </c>
       <c r="C514" s="3">
-        <v>2.9828180999999998</v>
+        <v>3.0072771999999999</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -6382,7 +6382,7 @@
         <v>10</v>
       </c>
       <c r="C515" s="3">
-        <v>2.9700470999999999</v>
+        <v>2.9944014999999999</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -6393,7 +6393,7 @@
         <v>11</v>
       </c>
       <c r="C516" s="3">
-        <v>2.9576250000000002</v>
+        <v>2.9818775</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -6404,7 +6404,7 @@
         <v>13</v>
       </c>
       <c r="C517" s="3">
-        <v>2.9394005000000001</v>
+        <v>2.9635036000000001</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -6415,7 +6415,7 @@
         <v>14</v>
       </c>
       <c r="C518" s="3">
-        <v>2.9250676000000002</v>
+        <v>2.9490531999999998</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -6426,7 +6426,7 @@
         <v>15</v>
       </c>
       <c r="C519" s="3">
-        <v>2.9128343000000001</v>
+        <v>2.9367195000000001</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -6437,7 +6437,7 @@
         <v>16</v>
       </c>
       <c r="C520" s="3">
-        <v>2.9000735999999998</v>
+        <v>2.9238542000000001</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -6448,7 +6448,7 @@
         <v>17</v>
       </c>
       <c r="C521" s="3">
-        <v>2.8925524999999999</v>
+        <v>2.9162713999999998</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -6459,7 +6459,7 @@
         <v>18</v>
       </c>
       <c r="C522" s="3">
-        <v>2.8850525</v>
+        <v>2.9087098999999998</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -6470,7 +6470,7 @@
         <v>19</v>
       </c>
       <c r="C523" s="3">
-        <v>2.8761361000000001</v>
+        <v>2.8997204000000001</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>20</v>
       </c>
       <c r="C524" s="3">
-        <v>2.8669616000000002</v>
+        <v>2.8904706999999998</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -6492,7 +6492,7 @@
         <v>21</v>
       </c>
       <c r="C525" s="3">
-        <v>2.8501447</v>
+        <v>2.8735159000000001</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -6503,7 +6503,7 @@
         <v>9</v>
       </c>
       <c r="C526" s="3">
-        <v>2.8430385999999999</v>
+        <v>2.8663514999999999</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -6514,7 +6514,7 @@
         <v>10</v>
       </c>
       <c r="C527" s="3">
-        <v>2.8345341999999998</v>
+        <v>2.8577773999999998</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -6525,7 +6525,7 @@
         <v>11</v>
       </c>
       <c r="C528" s="3">
-        <v>2.8223981999999999</v>
+        <v>2.8455419000000002</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -6536,7 +6536,7 @@
         <v>13</v>
       </c>
       <c r="C529" s="3">
-        <v>2.7952845000000002</v>
+        <v>2.8182057999999999</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -6547,7 +6547,7 @@
         <v>14</v>
       </c>
       <c r="C530" s="3">
-        <v>2.7761285</v>
+        <v>2.7988928</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -6558,7 +6558,7 @@
         <v>15</v>
       </c>
       <c r="C531" s="3">
-        <v>2.7628670999999998</v>
+        <v>2.7855226000000002</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -6569,7 +6569,7 @@
         <v>16</v>
       </c>
       <c r="C532" s="3">
-        <v>2.7488475999999999</v>
+        <v>2.7713882000000001</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -6580,7 +6580,7 @@
         <v>17</v>
       </c>
       <c r="C533" s="3">
-        <v>2.7313670000000001</v>
+        <v>2.7537642</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -6591,7 +6591,7 @@
         <v>18</v>
       </c>
       <c r="C534" s="3">
-        <v>2.7053946999999998</v>
+        <v>2.7275789000000001</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -6602,7 +6602,7 @@
         <v>19</v>
       </c>
       <c r="C535" s="3">
-        <v>2.6809978000000001</v>
+        <v>2.702982</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -6613,7 +6613,7 @@
         <v>20</v>
       </c>
       <c r="C536" s="3">
-        <v>2.6655380000000002</v>
+        <v>2.6873954000000002</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -6624,7 +6624,7 @@
         <v>21</v>
       </c>
       <c r="C537" s="3">
-        <v>2.6599525000000002</v>
+        <v>2.6817641000000001</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -6635,7 +6635,7 @@
         <v>9</v>
       </c>
       <c r="C538" s="3">
-        <v>2.6559677000000002</v>
+        <v>2.6777465999999999</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -6646,7 +6646,7 @@
         <v>10</v>
       </c>
       <c r="C539" s="3">
-        <v>2.6427543999999998</v>
+        <v>2.664425</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -6657,7 +6657,7 @@
         <v>11</v>
       </c>
       <c r="C540" s="3">
-        <v>2.6327497000000002</v>
+        <v>2.6543382000000002</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -6668,7 +6668,7 @@
         <v>13</v>
       </c>
       <c r="C541" s="3">
-        <v>2.6251369000000002</v>
+        <v>2.6466630000000002</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="C542" s="3">
-        <v>2.6084426999999999</v>
+        <v>2.6298319000000001</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -6690,7 +6690,7 @@
         <v>15</v>
       </c>
       <c r="C543" s="3">
-        <v>2.6003810000000001</v>
+        <v>2.6217041000000001</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -6701,7 +6701,7 @@
         <v>16</v>
       </c>
       <c r="C544" s="3">
-        <v>2.5951909999999998</v>
+        <v>2.6164716000000001</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -6712,7 +6712,7 @@
         <v>17</v>
       </c>
       <c r="C545" s="3">
-        <v>2.5809951</v>
+        <v>2.6021592999999998</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -6723,7 +6723,7 @@
         <v>18</v>
       </c>
       <c r="C546" s="3">
-        <v>2.5656026000000001</v>
+        <v>2.5866405000000001</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -6734,7 +6734,7 @@
         <v>19</v>
       </c>
       <c r="C547" s="3">
-        <v>2.5548715</v>
+        <v>2.5758214000000001</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -6745,7 +6745,7 @@
         <v>20</v>
       </c>
       <c r="C548" s="3">
-        <v>2.5490092</v>
+        <v>2.5699111000000001</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -6756,7 +6756,7 @@
         <v>21</v>
       </c>
       <c r="C549" s="3">
-        <v>2.5469710999999999</v>
+        <v>2.5678562999999999</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -6767,7 +6767,7 @@
         <v>9</v>
       </c>
       <c r="C550" s="3">
-        <v>2.5429032999999999</v>
+        <v>2.5637550999999998</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -6778,7 +6778,7 @@
         <v>10</v>
       </c>
       <c r="C551" s="3">
-        <v>2.5368151000000001</v>
+        <v>2.557617</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -6789,7 +6789,7 @@
         <v>11</v>
       </c>
       <c r="C552" s="3">
-        <v>2.5274624999999999</v>
+        <v>2.5481877000000002</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -6800,7 +6800,7 @@
         <v>13</v>
       </c>
       <c r="C553" s="3">
-        <v>2.5214116999999998</v>
+        <v>2.5420872999999999</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -6811,7 +6811,7 @@
         <v>14</v>
       </c>
       <c r="C554" s="3">
-        <v>2.4994166</v>
+        <v>2.5199118</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -6822,7 +6822,7 @@
         <v>15</v>
       </c>
       <c r="C555" s="3">
-        <v>2.4820422999999998</v>
+        <v>2.5023949999999999</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -6833,7 +6833,7 @@
         <v>16</v>
       </c>
       <c r="C556" s="3">
-        <v>2.4645442000000002</v>
+        <v>2.4847535000000001</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -6844,7 +6844,7 @@
         <v>17</v>
       </c>
       <c r="C557" s="3">
-        <v>2.4466831999999998</v>
+        <v>2.4667460000000001</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -6855,7 +6855,7 @@
         <v>18</v>
       </c>
       <c r="C558" s="3">
-        <v>2.4362083999999999</v>
+        <v>2.4561853</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -6866,7 +6866,7 @@
         <v>19</v>
       </c>
       <c r="C559" s="3">
-        <v>2.4388918999999998</v>
+        <v>2.4588907999999998</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -6877,7 +6877,7 @@
         <v>20</v>
       </c>
       <c r="C560" s="3">
-        <v>2.4405991999999999</v>
+        <v>2.4606121000000001</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -6888,7 +6888,7 @@
         <v>21</v>
       </c>
       <c r="C561" s="3">
-        <v>2.4423086999999999</v>
+        <v>2.4623355999999998</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -6899,7 +6899,7 @@
         <v>9</v>
       </c>
       <c r="C562" s="3">
-        <v>2.4291906999999999</v>
+        <v>2.4491101</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -6910,7 +6910,7 @@
         <v>10</v>
       </c>
       <c r="C563" s="3">
-        <v>2.4070466000000001</v>
+        <v>2.4267843999999998</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -6921,7 +6921,7 @@
         <v>11</v>
       </c>
       <c r="C564" s="3">
-        <v>2.3825067</v>
+        <v>2.4020432999999999</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -6932,7 +6932,7 @@
         <v>13</v>
       </c>
       <c r="C565" s="3">
-        <v>2.3682962000000001</v>
+        <v>2.3877161999999998</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -6943,7 +6943,7 @@
         <v>14</v>
       </c>
       <c r="C566" s="3">
-        <v>2.3462415999999999</v>
+        <v>2.3654807999999998</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -6954,7 +6954,7 @@
         <v>15</v>
       </c>
       <c r="C567" s="3">
-        <v>2.3336404000000002</v>
+        <v>2.3527762999999999</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -6965,7 +6965,7 @@
         <v>16</v>
       </c>
       <c r="C568" s="3">
-        <v>2.3183392999999999</v>
+        <v>2.3373496999999999</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -6976,7 +6976,7 @@
         <v>17</v>
       </c>
       <c r="C569" s="3">
-        <v>2.3017666999999999</v>
+        <v>2.3206411999999998</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -6987,7 +6987,7 @@
         <v>18</v>
       </c>
       <c r="C570" s="3">
-        <v>2.2887209999999998</v>
+        <v>2.3074884999999998</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -6998,7 +6998,7 @@
         <v>19</v>
       </c>
       <c r="C571" s="3">
-        <v>2.2836959999999999</v>
+        <v>2.3024222999999999</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -7009,7 +7009,7 @@
         <v>20</v>
       </c>
       <c r="C572" s="3">
-        <v>2.2836959999999999</v>
+        <v>2.3024222999999999</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -7020,7 +7020,7 @@
         <v>21</v>
       </c>
       <c r="C573" s="3">
-        <v>2.2741449999999999</v>
+        <v>2.2927930000000001</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -7031,7 +7031,7 @@
         <v>9</v>
       </c>
       <c r="C574" s="3">
-        <v>2.2639569000000002</v>
+        <v>2.2825213</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -7042,7 +7042,7 @@
         <v>10</v>
       </c>
       <c r="C575" s="3">
-        <v>2.2567360999999999</v>
+        <v>2.2752412999999998</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -7053,7 +7053,7 @@
         <v>11</v>
       </c>
       <c r="C576" s="3">
-        <v>2.2439448999999998</v>
+        <v>2.2623451999999999</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -7064,7 +7064,7 @@
         <v>13</v>
       </c>
       <c r="C577" s="3">
-        <v>2.2325598000000002</v>
+        <v>2.2508667999999998</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -7075,7 +7075,7 @@
         <v>14</v>
       </c>
       <c r="C578" s="3">
-        <v>2.2212307</v>
+        <v>2.2394447999999998</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -7086,7 +7086,7 @@
         <v>15</v>
       </c>
       <c r="C579" s="3">
-        <v>2.2126019000000001</v>
+        <v>2.2307451999999999</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -7097,7 +7097,7 @@
         <v>16</v>
       </c>
       <c r="C580" s="3">
-        <v>2.2086253999999998</v>
+        <v>2.2267361000000001</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
         <v>17</v>
       </c>
       <c r="C581" s="3">
-        <v>2.1945809000000001</v>
+        <v>2.2125764999999999</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -7119,7 +7119,7 @@
         <v>18</v>
       </c>
       <c r="C582" s="3">
-        <v>2.1825766</v>
+        <v>2.2004736999999999</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -7130,7 +7130,7 @@
         <v>19</v>
       </c>
       <c r="C583" s="3">
-        <v>2.1769162</v>
+        <v>2.1947668999999999</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -7141,7 +7141,7 @@
         <v>20</v>
       </c>
       <c r="C584" s="3">
-        <v>2.1675957000000001</v>
+        <v>2.1853699999999998</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -7152,7 +7152,7 @@
         <v>21</v>
       </c>
       <c r="C585" s="3">
-        <v>2.1578859000000001</v>
+        <v>2.1755806</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -7163,7 +7163,7 @@
         <v>9</v>
       </c>
       <c r="C586" s="3">
-        <v>2.144377</v>
+        <v>2.1619609</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -7174,7 +7174,7 @@
         <v>10</v>
       </c>
       <c r="C587" s="3">
-        <v>2.1292580999999999</v>
+        <v>2.1467179999999999</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -7185,7 +7185,7 @@
         <v>11</v>
       </c>
       <c r="C588" s="3">
-        <v>2.1178221000000002</v>
+        <v>2.1351882</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -7196,7 +7196,7 @@
         <v>13</v>
       </c>
       <c r="C589" s="3">
-        <v>2.1022650000000001</v>
+        <v>2.1195035999999998</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -7207,7 +7207,7 @@
         <v>14</v>
       </c>
       <c r="C590" s="3">
-        <v>2.0831010000000001</v>
+        <v>2.1001824</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -7218,7 +7218,7 @@
         <v>15</v>
       </c>
       <c r="C591" s="3">
-        <v>2.0723256000000001</v>
+        <v>2.0893187000000002</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -7229,7 +7229,7 @@
         <v>16</v>
       </c>
       <c r="C592" s="3">
-        <v>2.0599647999999999</v>
+        <v>2.0768564999999999</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -7240,7 +7240,7 @@
         <v>17</v>
       </c>
       <c r="C593" s="3">
-        <v>2.0478816000000002</v>
+        <v>2.0646741999999998</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -7251,7 +7251,7 @@
         <v>18</v>
       </c>
       <c r="C594" s="3">
-        <v>2.0407397999999999</v>
+        <v>2.0574739000000002</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -7262,7 +7262,7 @@
         <v>19</v>
       </c>
       <c r="C595" s="3">
-        <v>2.0350418000000001</v>
+        <v>2.0517291000000002</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
         <v>20</v>
       </c>
       <c r="C596" s="3">
-        <v>2.0376910000000001</v>
+        <v>2.0544001000000001</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -7284,7 +7284,7 @@
         <v>21</v>
       </c>
       <c r="C597" s="3">
-        <v>2.0344354</v>
+        <v>2.0511178000000001</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -7295,7 +7295,7 @@
         <v>9</v>
       </c>
       <c r="C598" s="3">
-        <v>2.0289575000000002</v>
+        <v>2.0455950000000001</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -7306,7 +7306,7 @@
         <v>10</v>
       </c>
       <c r="C599" s="3">
-        <v>2.0166553</v>
+        <v>2.0331918999999998</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -7317,7 +7317,7 @@
         <v>11</v>
       </c>
       <c r="C600" s="3">
-        <v>2.0058240000000001</v>
+        <v>2.0222718</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -7328,7 +7328,7 @@
         <v>13</v>
       </c>
       <c r="C601" s="3">
-        <v>1.9914852000000001</v>
+        <v>2.0078154000000001</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -7339,7 +7339,7 @@
         <v>14</v>
       </c>
       <c r="C602" s="3">
-        <v>1.9790175999999999</v>
+        <v>1.9952455</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -7350,7 +7350,7 @@
         <v>15</v>
       </c>
       <c r="C603" s="3">
-        <v>1.966432</v>
+        <v>1.9825566999999999</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -7361,7 +7361,7 @@
         <v>16</v>
       </c>
       <c r="C604" s="3">
-        <v>1.9504383000000001</v>
+        <v>1.9664318999999999</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -7372,7 +7372,7 @@
         <v>17</v>
       </c>
       <c r="C605" s="3">
-        <v>1.9353433</v>
+        <v>1.9512130999999999</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -7383,7 +7383,7 @@
         <v>18</v>
       </c>
       <c r="C606" s="3">
-        <v>1.9238004</v>
+        <v>1.9395756</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -7394,7 +7394,7 @@
         <v>19</v>
       </c>
       <c r="C607" s="3">
-        <v>1.9188118999999999</v>
+        <v>1.9345462</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -7405,7 +7405,7 @@
         <v>20</v>
       </c>
       <c r="C608" s="3">
-        <v>1.9163205000000001</v>
+        <v>1.9320343</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -7416,7 +7416,7 @@
         <v>21</v>
       </c>
       <c r="C609" s="3">
-        <v>1.9128776000000001</v>
+        <v>1.9285631999999999</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -7427,7 +7427,7 @@
         <v>9</v>
       </c>
       <c r="C610" s="3">
-        <v>1.9035493999999999</v>
+        <v>1.9191585</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -7438,7 +7438,7 @@
         <v>10</v>
       </c>
       <c r="C611" s="3">
-        <v>1.8963430999999999</v>
+        <v>1.9118930999999999</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -7449,7 +7449,7 @@
         <v>11</v>
       </c>
       <c r="C612" s="3">
-        <v>1.8863464000000001</v>
+        <v>1.9018143999999999</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -7460,7 +7460,7 @@
         <v>13</v>
       </c>
       <c r="C613" s="3">
-        <v>1.8747224</v>
+        <v>1.8900950999999999</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -7471,7 +7471,7 @@
         <v>14</v>
       </c>
       <c r="C614" s="3">
-        <v>1.8473818</v>
+        <v>1.8625303</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -7482,7 +7482,7 @@
         <v>15</v>
       </c>
       <c r="C615" s="3">
-        <v>1.8261974000000001</v>
+        <v>1.8411721999999999</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>16</v>
       </c>
       <c r="C616" s="3">
-        <v>1.7990325</v>
+        <v>1.8137846</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -7504,7 +7504,7 @@
         <v>17</v>
       </c>
       <c r="C617" s="3">
-        <v>1.7863492999999999</v>
+        <v>1.8009974</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -7515,7 +7515,7 @@
         <v>18</v>
       </c>
       <c r="C618" s="3">
-        <v>1.7688379000000001</v>
+        <v>1.7833424</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -7526,7 +7526,7 @@
         <v>19</v>
       </c>
       <c r="C619" s="3">
-        <v>1.7553211</v>
+        <v>1.7697147</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -7537,7 +7537,7 @@
         <v>20</v>
       </c>
       <c r="C620" s="3">
-        <v>1.7451992999999999</v>
+        <v>1.7595099000000001</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -7548,7 +7548,7 @@
         <v>21</v>
       </c>
       <c r="C621" s="3">
-        <v>1.7408473</v>
+        <v>1.7551222</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -7559,7 +7559,7 @@
         <v>9</v>
       </c>
       <c r="C622" s="3">
-        <v>1.7320141</v>
+        <v>1.7462165999999999</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -7570,7 +7570,7 @@
         <v>10</v>
       </c>
       <c r="C623" s="3">
-        <v>1.7187798999999999</v>
+        <v>1.7328739</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -7581,7 +7581,7 @@
         <v>11</v>
       </c>
       <c r="C624" s="3">
-        <v>1.6999105000000001</v>
+        <v>1.7138498</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -7592,7 +7592,7 @@
         <v>13</v>
       </c>
       <c r="C625" s="3">
-        <v>1.6847482</v>
+        <v>1.6985631000000001</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -7603,7 +7603,7 @@
         <v>14</v>
       </c>
       <c r="C626" s="3">
-        <v>1.6596861000000001</v>
+        <v>1.6732955</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -7614,7 +7614,7 @@
         <v>15</v>
       </c>
       <c r="C627" s="3">
-        <v>1.6440680000000001</v>
+        <v>1.6575494</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -7625,7 +7625,7 @@
         <v>16</v>
       </c>
       <c r="C628" s="3">
-        <v>1.6368663000000001</v>
+        <v>1.6502886000000001</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -7636,7 +7636,7 @@
         <v>17</v>
       </c>
       <c r="C629" s="3">
-        <v>1.6264559000000001</v>
+        <v>1.6397927999999999</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -7647,7 +7647,7 @@
         <v>18</v>
       </c>
       <c r="C630" s="3">
-        <v>1.6106714</v>
+        <v>1.6238789</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -7658,7 +7658,7 @@
         <v>19</v>
       </c>
       <c r="C631" s="3">
-        <v>1.6031367999999999</v>
+        <v>1.6162825000000001</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -7669,7 +7669,7 @@
         <v>20</v>
       </c>
       <c r="C632" s="3">
-        <v>1.5929424999999999</v>
+        <v>1.6060045999999999</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -7680,7 +7680,7 @@
         <v>21</v>
       </c>
       <c r="C633" s="3">
-        <v>1.5880190000000001</v>
+        <v>1.6010408</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -7691,7 +7691,7 @@
         <v>9</v>
       </c>
       <c r="C634" s="3">
-        <v>1.5867492999999999</v>
+        <v>1.5997606</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -7702,7 +7702,7 @@
         <v>10</v>
       </c>
       <c r="C635" s="3">
-        <v>1.5840573</v>
+        <v>1.5970466000000001</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
         <v>11</v>
       </c>
       <c r="C636" s="3">
-        <v>1.5829485000000001</v>
+        <v>1.5959287</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -7724,7 +7724,7 @@
         <v>13</v>
       </c>
       <c r="C637" s="3">
-        <v>1.5807355999999999</v>
+        <v>1.5936976</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -7735,7 +7735,7 @@
         <v>14</v>
       </c>
       <c r="C638" s="3">
-        <v>1.5741247</v>
+        <v>1.5870325000000001</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -7746,7 +7746,7 @@
         <v>15</v>
       </c>
       <c r="C639" s="3">
-        <v>1.5703552000000001</v>
+        <v>1.5832321</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -7757,7 +7757,7 @@
         <v>16</v>
       </c>
       <c r="C640" s="3">
-        <v>1.5653465</v>
+        <v>1.5781822999999999</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -7768,7 +7768,7 @@
         <v>17</v>
       </c>
       <c r="C641" s="3">
-        <v>1.5640954</v>
+        <v>1.576921</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -7779,7 +7779,7 @@
         <v>18</v>
       </c>
       <c r="C642" s="3">
-        <v>1.5584849999999999</v>
+        <v>1.5712645999999999</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -7790,7 +7790,7 @@
         <v>19</v>
       </c>
       <c r="C643" s="3">
-        <v>1.5631744000000001</v>
+        <v>1.5759924000000001</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -7801,7 +7801,7 @@
         <v>20</v>
       </c>
       <c r="C644" s="3">
-        <v>1.5605218000000001</v>
+        <v>1.5733181000000001</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -7812,7 +7812,7 @@
         <v>21</v>
       </c>
       <c r="C645" s="3">
-        <v>1.5609902</v>
+        <v>1.5737903</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -7823,7 +7823,7 @@
         <v>9</v>
       </c>
       <c r="C646" s="3">
-        <v>1.5613022000000001</v>
+        <v>1.5741049</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -7834,7 +7834,7 @@
         <v>10</v>
       </c>
       <c r="C647" s="3">
-        <v>1.5555464000000001</v>
+        <v>1.5683019</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -7845,7 +7845,7 @@
         <v>11</v>
       </c>
       <c r="C648" s="3">
-        <v>1.5527514</v>
+        <v>1.5654840000000001</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -7856,7 +7856,7 @@
         <v>13</v>
       </c>
       <c r="C649" s="3">
-        <v>1.5487249999999999</v>
+        <v>1.5614245</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -7867,7 +7867,7 @@
         <v>14</v>
       </c>
       <c r="C650" s="3">
-        <v>1.5451712</v>
+        <v>1.5578415999999999</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -7878,7 +7878,7 @@
         <v>15</v>
       </c>
       <c r="C651" s="3">
-        <v>1.5423941999999999</v>
+        <v>1.5550417999999999</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -7889,7 +7889,7 @@
         <v>16</v>
       </c>
       <c r="C652" s="3">
-        <v>1.5413158</v>
+        <v>1.5539546</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -7900,7 +7900,7 @@
         <v>17</v>
       </c>
       <c r="C653" s="3">
-        <v>1.5380852</v>
+        <v>1.5506975000000001</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -7911,7 +7911,7 @@
         <v>18</v>
       </c>
       <c r="C654" s="3">
-        <v>1.5315003</v>
+        <v>1.5440586000000001</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -7922,7 +7922,7 @@
         <v>19</v>
       </c>
       <c r="C655" s="3">
-        <v>1.5099085000000001</v>
+        <v>1.5222897</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -7933,7 +7933,7 @@
         <v>20</v>
       </c>
       <c r="C656" s="3">
-        <v>1.5061433</v>
+        <v>1.5184937000000001</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -7944,7 +7944,7 @@
         <v>21</v>
       </c>
       <c r="C657" s="3">
-        <v>1.5061433</v>
+        <v>1.5184937000000001</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -7955,7 +7955,7 @@
         <v>9</v>
       </c>
       <c r="C658" s="3">
-        <v>1.501638</v>
+        <v>1.5139514000000001</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -7966,7 +7966,7 @@
         <v>10</v>
       </c>
       <c r="C659" s="3">
-        <v>1.4956555</v>
+        <v>1.5079199000000001</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -7977,7 +7977,7 @@
         <v>11</v>
       </c>
       <c r="C660" s="3">
-        <v>1.4994046000000001</v>
+        <v>1.5116997000000001</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -7988,7 +7988,7 @@
         <v>13</v>
       </c>
       <c r="C661" s="3">
-        <v>1.4973078</v>
+        <v>1.5095856999999999</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -7999,7 +7999,7 @@
         <v>14</v>
       </c>
       <c r="C662" s="3">
-        <v>1.4919366999999999</v>
+        <v>1.5041705999999999</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -8010,7 +8010,7 @@
         <v>15</v>
       </c>
       <c r="C663" s="3">
-        <v>1.4839241999999999</v>
+        <v>1.4960924</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -8021,7 +8021,7 @@
         <v>16</v>
       </c>
       <c r="C664" s="3">
-        <v>1.4725845</v>
+        <v>1.4846596999999999</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>17</v>
       </c>
       <c r="C665" s="3">
-        <v>1.463802</v>
+        <v>1.4758051999999999</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -8043,7 +8043,7 @@
         <v>18</v>
       </c>
       <c r="C666" s="3">
-        <v>1.4616096000000001</v>
+        <v>1.4735948000000001</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -8054,7 +8054,7 @@
         <v>19</v>
       </c>
       <c r="C667" s="3">
-        <v>1.4614638</v>
+        <v>1.4734478</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
         <v>20</v>
       </c>
       <c r="C668" s="3">
-        <v>1.4600034</v>
+        <v>1.4719754</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -8076,7 +8076,7 @@
         <v>21</v>
       </c>
       <c r="C669" s="3">
-        <v>1.4582537</v>
+        <v>1.4702113999999999</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -8087,7 +8087,7 @@
         <v>9</v>
       </c>
       <c r="C670" s="3">
-        <v>1.4589828</v>
+        <v>1.4709464999999999</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -8098,7 +8098,7 @@
         <v>10</v>
       </c>
       <c r="C671" s="3">
-        <v>1.4584001</v>
+        <v>1.470359</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -8109,7 +8109,7 @@
         <v>11</v>
       </c>
       <c r="C672" s="3">
-        <v>1.4505668</v>
+        <v>1.4624614</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -8120,7 +8120,7 @@
         <v>13</v>
       </c>
       <c r="C673" s="3">
-        <v>1.4330830000000001</v>
+        <v>1.4448342999999999</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -8131,7 +8131,7 @@
         <v>14</v>
       </c>
       <c r="C674" s="3">
-        <v>1.4303652</v>
+        <v>1.4420942000000001</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -8142,7 +8142,7 @@
         <v>15</v>
       </c>
       <c r="C675" s="3">
-        <v>1.4279377</v>
+        <v>1.4396468</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
         <v>16</v>
       </c>
       <c r="C676" s="3">
-        <v>1.4253724999999999</v>
+        <v>1.4370605999999999</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -8164,7 +8164,7 @@
         <v>17</v>
       </c>
       <c r="C677" s="3">
-        <v>1.4286578999999999</v>
+        <v>1.4403729000000001</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -8175,7 +8175,7 @@
         <v>18</v>
       </c>
       <c r="C678" s="3">
-        <v>1.4322385</v>
+        <v>1.4439829</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -8186,7 +8186,7 @@
         <v>19</v>
       </c>
       <c r="C679" s="3">
-        <v>1.4279548</v>
+        <v>1.4396640000000001</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -8197,7 +8197,7 @@
         <v>20</v>
       </c>
       <c r="C680" s="3">
-        <v>1.421699</v>
+        <v>1.4333568999999999</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -8208,7 +8208,7 @@
         <v>21</v>
       </c>
       <c r="C681" s="3">
-        <v>1.4165992999999999</v>
+        <v>1.4282154</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -8219,7 +8219,7 @@
         <v>9</v>
       </c>
       <c r="C682" s="3">
-        <v>1.4043813999999999</v>
+        <v>1.4158972999999999</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="C683" s="3">
-        <v>1.3919925</v>
+        <v>1.4034068</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -8241,7 +8241,7 @@
         <v>11</v>
       </c>
       <c r="C684" s="3">
-        <v>1.3788936000000001</v>
+        <v>1.3902005</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -8252,7 +8252,7 @@
         <v>13</v>
       </c>
       <c r="C685" s="3">
-        <v>1.3590507999999999</v>
+        <v>1.3701950000000001</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -8263,7 +8263,7 @@
         <v>14</v>
       </c>
       <c r="C686" s="3">
-        <v>1.3553919000000001</v>
+        <v>1.3665061000000001</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -8274,7 +8274,7 @@
         <v>15</v>
       </c>
       <c r="C687" s="3">
-        <v>1.3443677999999999</v>
+        <v>1.3553915999999999</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -8285,7 +8285,7 @@
         <v>16</v>
       </c>
       <c r="C688" s="3">
-        <v>1.3329055000000001</v>
+        <v>1.3438353000000001</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -8296,7 +8296,7 @@
         <v>17</v>
       </c>
       <c r="C689" s="3">
-        <v>1.3278591</v>
+        <v>1.3387475</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -8307,7 +8307,7 @@
         <v>18</v>
       </c>
       <c r="C690" s="3">
-        <v>1.3152326000000001</v>
+        <v>1.3260175000000001</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -8318,7 +8318,7 @@
         <v>19</v>
       </c>
       <c r="C691" s="3">
-        <v>1.3073887</v>
+        <v>1.3181092999999999</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
@@ -8329,7 +8329,7 @@
         <v>20</v>
       </c>
       <c r="C692" s="3">
-        <v>1.2941875</v>
+        <v>1.3047998000000001</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
@@ -8340,7 +8340,7 @@
         <v>21</v>
       </c>
       <c r="C693" s="3">
-        <v>1.2828984000000001</v>
+        <v>1.2934182000000001</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
@@ -8351,7 +8351,7 @@
         <v>9</v>
       </c>
       <c r="C694" s="3">
-        <v>1.2676856999999999</v>
+        <v>1.2780807000000001</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
@@ -8362,7 +8362,7 @@
         <v>10</v>
       </c>
       <c r="C695" s="3">
-        <v>1.2531498000000001</v>
+        <v>1.2634255999999999</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
@@ -8373,7 +8373,7 @@
         <v>11</v>
       </c>
       <c r="C696" s="3">
-        <v>1.2427102000000001</v>
+        <v>1.2529003999999999</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
@@ -8384,7 +8384,7 @@
         <v>13</v>
       </c>
       <c r="C697" s="3">
-        <v>1.2337043000000001</v>
+        <v>1.2438206999999999</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
@@ -8395,7 +8395,7 @@
         <v>14</v>
       </c>
       <c r="C698" s="3">
-        <v>1.2254938</v>
+        <v>1.2355427999999999</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
@@ -8406,7 +8406,7 @@
         <v>15</v>
       </c>
       <c r="C699" s="3">
-        <v>1.2133602000000001</v>
+        <v>1.2233098</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
@@ -8417,7 +8417,7 @@
         <v>16</v>
       </c>
       <c r="C700" s="3">
-        <v>1.1929605999999999</v>
+        <v>1.2027429000000001</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
@@ -8428,7 +8428,7 @@
         <v>17</v>
       </c>
       <c r="C701" s="3">
-        <v>1.1806813</v>
+        <v>1.1903629</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
@@ -8439,7 +8439,7 @@
         <v>18</v>
       </c>
       <c r="C702" s="3">
-        <v>1.1753924</v>
+        <v>1.1850305999999999</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
@@ -8450,7 +8450,7 @@
         <v>19</v>
       </c>
       <c r="C703" s="3">
-        <v>1.1681497000000001</v>
+        <v>1.1777285</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
@@ -8461,7 +8461,7 @@
         <v>20</v>
       </c>
       <c r="C704" s="3">
-        <v>1.1752008</v>
+        <v>1.1848373999999999</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
@@ -8472,7 +8472,7 @@
         <v>21</v>
       </c>
       <c r="C705" s="3">
-        <v>1.178855</v>
+        <v>1.1885216000000001</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
@@ -8483,7 +8483,7 @@
         <v>9</v>
       </c>
       <c r="C706" s="3">
-        <v>1.1826399999999999</v>
+        <v>1.1923376000000001</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
@@ -8494,7 +8494,7 @@
         <v>10</v>
       </c>
       <c r="C707" s="3">
-        <v>1.1771073000000001</v>
+        <v>1.1867596</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
         <v>11</v>
       </c>
       <c r="C708" s="3">
-        <v>1.1726515</v>
+        <v>1.1822672000000001</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
@@ -8516,7 +8516,7 @@
         <v>13</v>
       </c>
       <c r="C709" s="3">
-        <v>1.1646154</v>
+        <v>1.1741652</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
@@ -8527,7 +8527,7 @@
         <v>14</v>
       </c>
       <c r="C710" s="3">
-        <v>1.1592823999999999</v>
+        <v>1.1687885</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
@@ -8538,7 +8538,7 @@
         <v>15</v>
       </c>
       <c r="C711" s="3">
-        <v>1.1504243000000001</v>
+        <v>1.1598577999999999</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
@@ -8549,7 +8549,7 @@
         <v>16</v>
       </c>
       <c r="C712" s="3">
-        <v>1.1431085999999999</v>
+        <v>1.1524821000000001</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
@@ -8560,7 +8560,7 @@
         <v>17</v>
       </c>
       <c r="C713" s="3">
-        <v>1.1370822</v>
+        <v>1.1464063</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
@@ -8571,7 +8571,7 @@
         <v>18</v>
       </c>
       <c r="C714" s="3">
-        <v>1.1330032000000001</v>
+        <v>1.1422938</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
@@ -8582,7 +8582,7 @@
         <v>19</v>
       </c>
       <c r="C715" s="3">
-        <v>1.1341371</v>
+        <v>1.143437</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>20</v>
       </c>
       <c r="C716" s="3">
-        <v>1.135159</v>
+        <v>1.1444673000000001</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
@@ -8604,7 +8604,7 @@
         <v>21</v>
       </c>
       <c r="C717" s="3">
-        <v>1.1328932</v>
+        <v>1.1421828999999999</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
@@ -8615,7 +8615,7 @@
         <v>9</v>
       </c>
       <c r="C718" s="3">
-        <v>1.1316489000000001</v>
+        <v>1.1409284</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
@@ -8626,7 +8626,7 @@
         <v>10</v>
       </c>
       <c r="C719" s="3">
-        <v>1.1302920999999999</v>
+        <v>1.1395605</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
@@ -8637,7 +8637,7 @@
         <v>11</v>
       </c>
       <c r="C720" s="3">
-        <v>1.1291628</v>
+        <v>1.1384219</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
@@ -8648,7 +8648,7 @@
         <v>13</v>
       </c>
       <c r="C721" s="3">
-        <v>1.1229864000000001</v>
+        <v>1.1321949</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.25">
@@ -8659,7 +8659,7 @@
         <v>14</v>
       </c>
       <c r="C722" s="3">
-        <v>1.1166218000000001</v>
+        <v>1.1257781</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.25">
@@ -8670,7 +8670,7 @@
         <v>15</v>
       </c>
       <c r="C723" s="3">
-        <v>1.10765</v>
+        <v>1.1167327</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.25">
@@ -8681,7 +8681,7 @@
         <v>16</v>
       </c>
       <c r="C724" s="3">
-        <v>1.1055491</v>
+        <v>1.1146145999999999</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
@@ -8692,7 +8692,7 @@
         <v>17</v>
       </c>
       <c r="C725" s="3">
-        <v>1.1014740000000001</v>
+        <v>1.1105061000000001</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.25">
@@ -8703,7 +8703,7 @@
         <v>18</v>
       </c>
       <c r="C726" s="3">
-        <v>1.0964303</v>
+        <v>1.105421</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.25">
@@ -8714,7 +8714,7 @@
         <v>19</v>
       </c>
       <c r="C727" s="3">
-        <v>1.0936961999999999</v>
+        <v>1.1026644999999999</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.25">
@@ -8725,7 +8725,7 @@
         <v>20</v>
       </c>
       <c r="C728" s="3">
-        <v>1.0908599000000001</v>
+        <v>1.0998049999999999</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.25">
@@ -8736,7 +8736,7 @@
         <v>21</v>
       </c>
       <c r="C729" s="3">
-        <v>1.0923890000000001</v>
+        <v>1.1013466000000001</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.25">
@@ -8747,7 +8747,7 @@
         <v>9</v>
       </c>
       <c r="C730" s="3">
-        <v>1.0871705</v>
+        <v>1.0960852999999999</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.25">
@@ -8758,7 +8758,7 @@
         <v>10</v>
       </c>
       <c r="C731" s="3">
-        <v>1.0805792999999999</v>
+        <v>1.0894401</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.25">
@@ -8769,7 +8769,7 @@
         <v>11</v>
       </c>
       <c r="C732" s="3">
-        <v>1.0770246999999999</v>
+        <v>1.0858563000000001</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.25">
@@ -8780,7 +8780,7 @@
         <v>13</v>
       </c>
       <c r="C733" s="3">
-        <v>1.0718799999999999</v>
+        <v>1.0806693999999999</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.25">
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="C734" s="3">
-        <v>1.0718799999999999</v>
+        <v>1.0806693999999999</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.25">
@@ -8802,7 +8802,7 @@
         <v>15</v>
       </c>
       <c r="C735" s="3">
-        <v>1.0562475</v>
+        <v>1.0649086999999999</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>16</v>
       </c>
       <c r="C736" s="3">
-        <v>1.0508881000000001</v>
+        <v>1.0595053999999999</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.25">
@@ -8824,7 +8824,7 @@
         <v>17</v>
       </c>
       <c r="C737" s="3">
-        <v>1.0458677999999999</v>
+        <v>1.0544439000000001</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.25">
@@ -8835,7 +8835,7 @@
         <v>18</v>
       </c>
       <c r="C738" s="3">
-        <v>1.0422197</v>
+        <v>1.0507659</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
@@ -8846,7 +8846,7 @@
         <v>19</v>
       </c>
       <c r="C739" s="3">
-        <v>1.0398284</v>
+        <v>1.0483549999999999</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
@@ -8857,7 +8857,7 @@
         <v>20</v>
       </c>
       <c r="C740" s="3">
-        <v>1.0376493</v>
+        <v>1.0461579999999999</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.25">
@@ -8868,7 +8868,7 @@
         <v>21</v>
       </c>
       <c r="C741" s="3">
-        <v>1.0398331999999999</v>
+        <v>1.0483598000000001</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.25">
@@ -8879,7 +8879,7 @@
         <v>9</v>
       </c>
       <c r="C742" s="3">
-        <v>1.0344538000000001</v>
+        <v>1.0429363</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.25">
@@ -8890,7 +8890,7 @@
         <v>10</v>
       </c>
       <c r="C743" s="3">
-        <v>1.0341435000000001</v>
+        <v>1.0426234999999999</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.25">
@@ -8901,7 +8901,7 @@
         <v>11</v>
       </c>
       <c r="C744" s="3">
-        <v>1.0338334</v>
+        <v>1.0423108000000001</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.25">
@@ -8912,7 +8912,7 @@
         <v>13</v>
       </c>
       <c r="C745" s="3">
-        <v>1.0316668</v>
+        <v>1.0401265</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.25">
@@ -8923,7 +8923,7 @@
         <v>14</v>
       </c>
       <c r="C746" s="3">
-        <v>1.0276590999999999</v>
+        <v>1.0360859</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.25">
@@ -8934,7 +8934,7 @@
         <v>15</v>
       </c>
       <c r="C747" s="3">
-        <v>1.0219362000000001</v>
+        <v>1.0303161000000001</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.25">
@@ -8945,7 +8945,7 @@
         <v>16</v>
       </c>
       <c r="C748" s="3">
-        <v>1.0127204999999999</v>
+        <v>1.0210248</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.25">
@@ -8956,7 +8956,7 @@
         <v>17</v>
       </c>
       <c r="C749" s="3">
-        <v>1.0045833</v>
+        <v>1.0128208999999999</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.25">
@@ -8967,7 +8967,7 @@
         <v>18</v>
       </c>
       <c r="C750" s="3">
-        <v>0.99809570000000003</v>
+        <v>1.0062800999999999</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.25">
@@ -8978,7 +8978,7 @@
         <v>19</v>
       </c>
       <c r="C751" s="3">
-        <v>0.99670029999999998</v>
+        <v>1.0048732</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.25">
@@ -8989,7 +8989,18 @@
         <v>20</v>
       </c>
       <c r="C752" s="3">
-        <v>0.99680000000000002</v>
+        <v>1.0049737999999999</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A753" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B753" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C753" s="3">
+        <v>1.0082</v>
       </c>
     </row>
   </sheetData>
